--- a/Bitacora_10.xlsx
+++ b/Bitacora_10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://btgpactual-my.sharepoint.com/personal/juan_alcala_btgpactual_com/Documents/Escritorio/Bitacoras/bitacoras/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://btgpactual-my.sharepoint.com/personal/juan_alcala_btgpactual_com/Documents/Bitacoras/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="433" documentId="8_{B11B8281-ACE1-4350-8618-021BE984FAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41AEFD08-6A10-4AA7-86A1-B29CF42E7D14}"/>
+  <xr:revisionPtr revIDLastSave="456" documentId="8_{B11B8281-ACE1-4350-8618-021BE984FAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47DC3E3A-2816-47B5-AA35-FC2DD4921CAD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18615" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="235">
   <si>
     <t>Código: 
 GFPI-F-147</t>
@@ -508,6 +508,9 @@
     <t>BTG Pactual</t>
   </si>
   <si>
+    <t xml:space="preserve">Desde 15/02/2026  hasta 28/02/2025 </t>
+  </si>
+  <si>
     <t xml:space="preserve">Santiago Pulgarin Vazquez </t>
   </si>
   <si>
@@ -673,6 +676,102 @@
     <t xml:space="preserve">Y/O COMENTARIOS  REALIZADOS POR LAS PERSONAS CON ROL DE: APRENDIZ Y/O JEFE INMEDIATO </t>
   </si>
   <si>
+    <t>Modifiqué la consulta de operaciones para que se añadieran los datos de operaciones manuales</t>
+  </si>
+  <si>
+    <t>Los cambios fueron integrados y subidos al repositorio en Azure</t>
+  </si>
+  <si>
+    <t>No se presentaron dificultades</t>
+  </si>
+  <si>
+    <t>Registré una funcion para identificar los datos que recivia desde AWS</t>
+  </si>
+  <si>
+    <t>El funcion fue implementado y validado en la lambda de AWS</t>
+  </si>
+  <si>
+    <t>Actividad exploratoria</t>
+  </si>
+  <si>
+    <t>Eliminé el log que mostraba el contexto y corregí la tabulación de la consulta</t>
+  </si>
+  <si>
+    <t>Ajustes confirmados y subidos al repositorio en Azure</t>
+  </si>
+  <si>
+    <t>Mejoré la legibilidad del código</t>
+  </si>
+  <si>
+    <t>Estandaricé la convención de nombres de servicios en CoreConstants y servicios relacionados</t>
+  </si>
+  <si>
+    <t>Los cambios fueron aplicados y registrados en Azure</t>
+  </si>
+  <si>
+    <t>Uniformidad lograda</t>
+  </si>
+  <si>
+    <t>Actualicé la convención de nombres de servicios en CoreConstants y servicios relacionados</t>
+  </si>
+  <si>
+    <t>Los ajustes quedaron integrados en el repositorio</t>
+  </si>
+  <si>
+    <t>Cambios menores</t>
+  </si>
+  <si>
+    <t>Corregí la visualización de la cuenta omnibus en el front-end</t>
+  </si>
+  <si>
+    <t>La corrección fue subida y validada en Azure</t>
+  </si>
+  <si>
+    <t>Validación completada</t>
+  </si>
+  <si>
+    <t>Modifiqué las pruebas unitarias de operaciones</t>
+  </si>
+  <si>
+    <t>Las pruebas corregidas quedaron registradas en el repositorio</t>
+  </si>
+  <si>
+    <t>Validación exitosa</t>
+  </si>
+  <si>
+    <t>Refactoricé la ubicación del componente omnibus y actualicé las importaciones</t>
+  </si>
+  <si>
+    <t>Los cambios fueron reorganizados y subidos en Azure</t>
+  </si>
+  <si>
+    <t>Reestructuración completada</t>
+  </si>
+  <si>
+    <t>Ajusté el filtro de especies</t>
+  </si>
+  <si>
+    <t>La modificación fue aplicada y subida al repositorio</t>
+  </si>
+  <si>
+    <t>Añadí una consulta SQL con union para operaciones manuales en la función associated_cdt_investors</t>
+  </si>
+  <si>
+    <t>La nueva consulta quedó implementada y registrada en Azure</t>
+  </si>
+  <si>
+    <t>Integración realizada con éxito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estuve ocasionalemnete ayudando a mis compañeros en sus prosesos </t>
+  </si>
+  <si>
+    <t>Colaboraciones registradas en repositorio y comunicación interna</t>
+  </si>
+  <si>
+    <t>Apoyo puntual, sin dificultades</t>
+  </si>
+  <si>
     <t xml:space="preserve">Decreto 055 de 2015, por el cual se reglamenta la afiliación de estudiantes al Sistema General de Riesgos Laborales y se dictan otras disposiciones </t>
   </si>
   <si>
@@ -844,102 +943,12 @@
   <si>
     <t>firma el instructor que recibe la bitácora</t>
   </si>
-  <si>
-    <t xml:space="preserve">Desde 15/02/2026  hasta 28/02/2025 </t>
-  </si>
-  <si>
-    <t>Modifiqué la consulta de operaciones para que se añadieran los datos de operaciones manuales</t>
-  </si>
-  <si>
-    <t>Eliminé el log que mostraba el contexto y corregí la tabulación de la consulta</t>
-  </si>
-  <si>
-    <t>Estandaricé la convención de nombres de servicios en CoreConstants y servicios relacionados</t>
-  </si>
-  <si>
-    <t>Registré una funcion para identificar los datos que recivia desde AWS</t>
-  </si>
-  <si>
-    <t>Actualicé la convención de nombres de servicios en CoreConstants y servicios relacionados</t>
-  </si>
-  <si>
-    <t>Corregí la visualización de la cuenta omnibus en el front-end</t>
-  </si>
-  <si>
-    <t>Modifiqué las pruebas unitarias de operaciones</t>
-  </si>
-  <si>
-    <t>Refactoricé la ubicación del componente omnibus y actualicé las importaciones</t>
-  </si>
-  <si>
-    <t>Ajusté el filtro de especies</t>
-  </si>
-  <si>
-    <t>Añadí una consulta SQL con union para operaciones manuales en la función associated_cdt_investors</t>
-  </si>
-  <si>
-    <t>Los cambios fueron integrados y subidos al repositorio en Azure</t>
-  </si>
-  <si>
-    <t>Ajustes confirmados y subidos al repositorio en Azure</t>
-  </si>
-  <si>
-    <t>Los cambios fueron aplicados y registrados en Azure</t>
-  </si>
-  <si>
-    <t>El funcion fue implementado y validado en la lambda de AWS</t>
-  </si>
-  <si>
-    <t>Los ajustes quedaron integrados en el repositorio</t>
-  </si>
-  <si>
-    <t>La corrección fue subida y validada en Azure</t>
-  </si>
-  <si>
-    <t>Las pruebas corregidas quedaron registradas en el repositorio</t>
-  </si>
-  <si>
-    <t>Los cambios fueron reorganizados y subidos en Azure</t>
-  </si>
-  <si>
-    <t>La modificación fue aplicada y subida al repositorio</t>
-  </si>
-  <si>
-    <t>La nueva consulta quedó implementada y registrada en Azure</t>
-  </si>
-  <si>
-    <t>No se presentaron dificultades</t>
-  </si>
-  <si>
-    <t>Actividad exploratoria</t>
-  </si>
-  <si>
-    <t>Mejoré la legibilidad del código</t>
-  </si>
-  <si>
-    <t>Uniformidad lograda</t>
-  </si>
-  <si>
-    <t>Cambios menores</t>
-  </si>
-  <si>
-    <t>Validación completada</t>
-  </si>
-  <si>
-    <t>Validación exitosa</t>
-  </si>
-  <si>
-    <t>Reestructuración completada</t>
-  </si>
-  <si>
-    <t>Integración realizada con éxito</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2307,7 +2316,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="282">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2796,6 +2805,48 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2808,6 +2859,45 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2859,174 +2949,183 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="52" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="52" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3045,83 +3144,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3668,13 +3692,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1756833</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>179917</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1629834</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>137582</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3717,22 +3741,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1131092</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>71437</xdr:rowOff>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1035843</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>157162</xdr:rowOff>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="Imagen 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11B3F5F4-4BF6-45A5-9845-6432BCF13C59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A443F7DF-CCF4-91FF-2BD4-375356FA483E}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
               <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{9F75D9DB-16BF-493F-916C-CBC4DAF8756A}"/>
@@ -3751,8 +3775,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10001248" y="25348406"/>
-          <a:ext cx="2083595" cy="466725"/>
+          <a:off x="10106025" y="26355675"/>
+          <a:ext cx="1619250" cy="419100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4131,7 +4155,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:H59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" customWidth="1"/>
     <col min="2" max="2" width="47.42578125" style="58" customWidth="1"/>
@@ -4141,7 +4165,7 @@
     <col min="7" max="7" width="46.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="28.5" customHeight="1">
       <c r="B1" s="67"/>
       <c r="C1" s="68"/>
       <c r="D1" s="68"/>
@@ -4152,7 +4176,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
     </row>
-    <row r="2" spans="2:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="28.5" customHeight="1">
       <c r="B2" s="70"/>
       <c r="C2" s="54"/>
       <c r="D2" s="54"/>
@@ -4163,582 +4187,582 @@
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="172" t="s">
+    <row r="3" spans="2:8" ht="25.5" customHeight="1">
+      <c r="B3" s="199" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="174"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="201"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="175" t="s">
+    <row r="4" spans="2:8" ht="25.5" customHeight="1">
+      <c r="B4" s="202" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="176"/>
-      <c r="D4" s="176"/>
-      <c r="E4" s="177"/>
+      <c r="C4" s="203"/>
+      <c r="D4" s="203"/>
+      <c r="E4" s="204"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="178" t="s">
+    <row r="5" spans="2:8" ht="25.5" customHeight="1">
+      <c r="B5" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="179"/>
-      <c r="D5" s="179"/>
-      <c r="E5" s="180"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="206"/>
+      <c r="E5" s="207"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="175" t="s">
+    <row r="6" spans="2:8" ht="25.5" customHeight="1">
+      <c r="B6" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="177"/>
+      <c r="C6" s="203"/>
+      <c r="D6" s="203"/>
+      <c r="E6" s="204"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="172" t="s">
+    <row r="7" spans="2:8" ht="25.5" customHeight="1">
+      <c r="B7" s="199" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="173"/>
-      <c r="D7" s="173"/>
-      <c r="E7" s="174"/>
+      <c r="C7" s="200"/>
+      <c r="D7" s="200"/>
+      <c r="E7" s="201"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="2:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" ht="31.5" customHeight="1">
       <c r="B8" s="72" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="181" t="s">
+      <c r="D8" s="208" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="182"/>
+      <c r="E8" s="209"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="183" t="s">
+    <row r="9" spans="2:8" ht="25.5" customHeight="1">
+      <c r="B9" s="210" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="184"/>
-      <c r="D9" s="184"/>
-      <c r="E9" s="185"/>
+      <c r="C9" s="211"/>
+      <c r="D9" s="211"/>
+      <c r="E9" s="212"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="2:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="186" t="s">
+    <row r="10" spans="2:8" ht="17.25" customHeight="1">
+      <c r="B10" s="213" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="187"/>
-      <c r="D10" s="187"/>
-      <c r="E10" s="188"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="189" t="s">
+      <c r="C10" s="214"/>
+      <c r="D10" s="214"/>
+      <c r="E10" s="215"/>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" s="191" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="190"/>
-      <c r="D11" s="190"/>
-      <c r="E11" s="191"/>
-    </row>
-    <row r="12" spans="2:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="168" t="s">
+      <c r="C11" s="192"/>
+      <c r="D11" s="192"/>
+      <c r="E11" s="193"/>
+    </row>
+    <row r="12" spans="2:8" ht="51" customHeight="1">
+      <c r="B12" s="182" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="169"/>
-      <c r="D12" s="170"/>
-      <c r="E12" s="171"/>
+      <c r="C12" s="183"/>
+      <c r="D12" s="184"/>
+      <c r="E12" s="185"/>
       <c r="F12" s="1"/>
       <c r="G12" s="36"/>
     </row>
-    <row r="13" spans="2:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" ht="12.75" customHeight="1">
       <c r="B13" s="78"/>
       <c r="C13" s="79"/>
       <c r="D13" s="79"/>
       <c r="E13" s="80"/>
     </row>
-    <row r="14" spans="2:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="201" t="s">
+    <row r="14" spans="2:8" ht="27.75" customHeight="1">
+      <c r="B14" s="173" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="202"/>
-      <c r="D14" s="202"/>
-      <c r="E14" s="203"/>
-    </row>
-    <row r="15" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="204" t="s">
+      <c r="C14" s="174"/>
+      <c r="D14" s="174"/>
+      <c r="E14" s="175"/>
+    </row>
+    <row r="15" spans="2:8" ht="21.75" customHeight="1">
+      <c r="B15" s="176" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="205"/>
-      <c r="D15" s="205"/>
-      <c r="E15" s="206"/>
-    </row>
-    <row r="16" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="204" t="s">
+      <c r="C15" s="177"/>
+      <c r="D15" s="177"/>
+      <c r="E15" s="178"/>
+    </row>
+    <row r="16" spans="2:8" ht="21.75" customHeight="1">
+      <c r="B16" s="176" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="205"/>
-      <c r="D16" s="205"/>
-      <c r="E16" s="206"/>
-    </row>
-    <row r="17" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="210" t="s">
+      <c r="C16" s="177"/>
+      <c r="D16" s="177"/>
+      <c r="E16" s="178"/>
+    </row>
+    <row r="17" spans="2:6" ht="30" customHeight="1">
+      <c r="B17" s="186" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="211"/>
-      <c r="D17" s="211"/>
-      <c r="E17" s="212"/>
-    </row>
-    <row r="18" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="204" t="s">
+      <c r="C17" s="187"/>
+      <c r="D17" s="187"/>
+      <c r="E17" s="188"/>
+    </row>
+    <row r="18" spans="2:6" ht="21.75" customHeight="1">
+      <c r="B18" s="176" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="205"/>
-      <c r="D18" s="205"/>
-      <c r="E18" s="206"/>
-    </row>
-    <row r="19" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="204" t="s">
+      <c r="C18" s="177"/>
+      <c r="D18" s="177"/>
+      <c r="E18" s="178"/>
+    </row>
+    <row r="19" spans="2:6" ht="21.75" customHeight="1">
+      <c r="B19" s="176" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="205"/>
-      <c r="D19" s="205"/>
-      <c r="E19" s="206"/>
-    </row>
-    <row r="20" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="207" t="s">
+      <c r="C19" s="177"/>
+      <c r="D19" s="177"/>
+      <c r="E19" s="178"/>
+    </row>
+    <row r="20" spans="2:6" ht="21.75" customHeight="1">
+      <c r="B20" s="179" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="208"/>
-      <c r="D20" s="208"/>
-      <c r="E20" s="209"/>
-    </row>
-    <row r="21" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="168" t="s">
+      <c r="C20" s="180"/>
+      <c r="D20" s="180"/>
+      <c r="E20" s="181"/>
+    </row>
+    <row r="21" spans="2:6" ht="27" customHeight="1">
+      <c r="B21" s="182" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="169"/>
-      <c r="D21" s="170"/>
-      <c r="E21" s="171"/>
-    </row>
-    <row r="22" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="189" t="s">
+      <c r="C21" s="183"/>
+      <c r="D21" s="184"/>
+      <c r="E21" s="185"/>
+    </row>
+    <row r="22" spans="2:6" ht="15" customHeight="1">
+      <c r="B22" s="191" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="190"/>
-      <c r="D22" s="190" t="s">
+      <c r="C22" s="192"/>
+      <c r="D22" s="192" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="191"/>
-    </row>
-    <row r="23" spans="2:6" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="192"/>
-      <c r="C23" s="193"/>
-      <c r="D23" s="193"/>
-      <c r="E23" s="194"/>
-    </row>
-    <row r="24" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E22" s="193"/>
+    </row>
+    <row r="23" spans="2:6" ht="5.25" customHeight="1">
+      <c r="B23" s="194"/>
+      <c r="C23" s="195"/>
+      <c r="D23" s="195"/>
+      <c r="E23" s="196"/>
+    </row>
+    <row r="24" spans="2:6" ht="14.25" customHeight="1">
       <c r="B24" s="73" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="195" t="s">
+      <c r="D24" s="197" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="196"/>
+      <c r="E24" s="198"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6">
       <c r="B25" s="74" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="197"/>
-      <c r="E25" s="198"/>
-    </row>
-    <row r="26" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="D25" s="189"/>
+      <c r="E25" s="190"/>
+    </row>
+    <row r="26" spans="2:6" ht="31.5">
       <c r="B26" s="62" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="197"/>
-      <c r="E26" s="198"/>
-    </row>
-    <row r="27" spans="2:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="D26" s="189"/>
+      <c r="E26" s="190"/>
+    </row>
+    <row r="27" spans="2:6" ht="45">
       <c r="B27" s="64" t="s">
         <v>30</v>
       </c>
       <c r="C27" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="197"/>
-      <c r="E27" s="198"/>
-    </row>
-    <row r="28" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D27" s="189"/>
+      <c r="E27" s="190"/>
+    </row>
+    <row r="28" spans="2:6" ht="21" customHeight="1">
       <c r="B28" s="74" t="s">
         <v>32</v>
       </c>
       <c r="C28" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="197"/>
-      <c r="E28" s="198"/>
-    </row>
-    <row r="29" spans="2:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="189"/>
+      <c r="E28" s="190"/>
+    </row>
+    <row r="29" spans="2:6" ht="44.25" customHeight="1">
       <c r="B29" s="74" t="s">
         <v>34</v>
       </c>
       <c r="C29" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="D29" s="197" t="s">
+      <c r="D29" s="189" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="198" t="s">
+      <c r="E29" s="190" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" ht="36.75" customHeight="1">
       <c r="B30" s="74" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="197" t="s">
+      <c r="D30" s="189" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="198" t="s">
+      <c r="E30" s="190" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" ht="30">
       <c r="B31" s="74" t="s">
         <v>40</v>
       </c>
       <c r="C31" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="197"/>
-      <c r="E31" s="198"/>
-    </row>
-    <row r="32" spans="2:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="189"/>
+      <c r="E31" s="190"/>
+    </row>
+    <row r="32" spans="2:6" ht="65.25" customHeight="1">
       <c r="B32" s="74" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="197" t="s">
+      <c r="D32" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="198" t="s">
+      <c r="E32" s="190" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" ht="75">
       <c r="B33" s="74" t="s">
         <v>45</v>
       </c>
       <c r="C33" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="197"/>
-      <c r="E33" s="198"/>
-    </row>
-    <row r="34" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="D33" s="189"/>
+      <c r="E33" s="190"/>
+    </row>
+    <row r="34" spans="2:5" ht="60">
       <c r="B34" s="74" t="s">
         <v>47</v>
       </c>
       <c r="C34" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="197"/>
-      <c r="E34" s="198"/>
-    </row>
-    <row r="35" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="D34" s="189"/>
+      <c r="E34" s="190"/>
+    </row>
+    <row r="35" spans="2:5" ht="60">
       <c r="B35" s="74" t="s">
         <v>49</v>
       </c>
       <c r="C35" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="197"/>
-      <c r="E35" s="198"/>
-    </row>
-    <row r="36" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="D35" s="189"/>
+      <c r="E35" s="190"/>
+    </row>
+    <row r="36" spans="2:5" ht="45">
       <c r="B36" s="74" t="s">
         <v>51</v>
       </c>
       <c r="C36" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="D36" s="197"/>
-      <c r="E36" s="198"/>
-    </row>
-    <row r="37" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="D36" s="189"/>
+      <c r="E36" s="190"/>
+    </row>
+    <row r="37" spans="2:5" ht="60">
       <c r="B37" s="74" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="197"/>
-      <c r="E37" s="198"/>
-    </row>
-    <row r="38" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="D37" s="189"/>
+      <c r="E37" s="190"/>
+    </row>
+    <row r="38" spans="2:5" ht="60">
       <c r="B38" s="74" t="s">
         <v>55</v>
       </c>
       <c r="C38" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="197"/>
-      <c r="E38" s="198"/>
-    </row>
-    <row r="39" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="D38" s="189"/>
+      <c r="E38" s="190"/>
+    </row>
+    <row r="39" spans="2:5" ht="60">
       <c r="B39" s="74" t="s">
         <v>32</v>
       </c>
       <c r="C39" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="D39" s="197"/>
-      <c r="E39" s="198"/>
-    </row>
-    <row r="40" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="D39" s="189"/>
+      <c r="E39" s="190"/>
+    </row>
+    <row r="40" spans="2:5" ht="60">
       <c r="B40" s="74" t="s">
         <v>58</v>
       </c>
       <c r="C40" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="D40" s="197"/>
-      <c r="E40" s="198"/>
-    </row>
-    <row r="41" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="D40" s="189"/>
+      <c r="E40" s="190"/>
+    </row>
+    <row r="41" spans="2:5" ht="60">
       <c r="B41" s="74" t="s">
         <v>60</v>
       </c>
       <c r="C41" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="197"/>
-      <c r="E41" s="198"/>
-    </row>
-    <row r="42" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="D41" s="189"/>
+      <c r="E41" s="190"/>
+    </row>
+    <row r="42" spans="2:5" ht="60">
       <c r="B42" s="74" t="s">
         <v>58</v>
       </c>
       <c r="C42" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="D42" s="197"/>
-      <c r="E42" s="198"/>
-    </row>
-    <row r="43" spans="2:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="D42" s="189"/>
+      <c r="E42" s="190"/>
+    </row>
+    <row r="43" spans="2:5" ht="409.5">
       <c r="B43" s="74" t="s">
         <v>63</v>
       </c>
       <c r="C43" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="D43" s="197" t="s">
+      <c r="D43" s="189" t="s">
         <v>65</v>
       </c>
-      <c r="E43" s="198" t="s">
+      <c r="E43" s="190" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" ht="30">
       <c r="B44" s="74" t="s">
         <v>66</v>
       </c>
       <c r="C44" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="197"/>
-      <c r="E44" s="198"/>
-    </row>
-    <row r="45" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="D44" s="189"/>
+      <c r="E44" s="190"/>
+    </row>
+    <row r="45" spans="2:5" ht="30">
       <c r="B45" s="74" t="s">
         <v>68</v>
       </c>
       <c r="C45" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="D45" s="197"/>
-      <c r="E45" s="198"/>
-    </row>
-    <row r="46" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="D45" s="189"/>
+      <c r="E45" s="190"/>
+    </row>
+    <row r="46" spans="2:5" ht="30">
       <c r="B46" s="74" t="s">
         <v>70</v>
       </c>
       <c r="C46" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="D46" s="197"/>
-      <c r="E46" s="198"/>
-    </row>
-    <row r="47" spans="2:5" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D46" s="189"/>
+      <c r="E46" s="190"/>
+    </row>
+    <row r="47" spans="2:5" ht="127.5" customHeight="1">
       <c r="B47" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C47" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="D47" s="197" t="s">
+      <c r="D47" s="189" t="s">
         <v>74</v>
       </c>
-      <c r="E47" s="198" t="s">
+      <c r="E47" s="190" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" ht="45">
       <c r="B48" s="74" t="s">
         <v>75</v>
       </c>
       <c r="C48" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="197"/>
-      <c r="E48" s="198"/>
-    </row>
-    <row r="49" spans="2:5" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D48" s="189"/>
+      <c r="E48" s="190"/>
+    </row>
+    <row r="49" spans="2:5" ht="146.25" customHeight="1">
       <c r="B49" s="74" t="s">
         <v>77</v>
       </c>
       <c r="C49" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="197" t="s">
+      <c r="D49" s="189" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="198" t="s">
+      <c r="E49" s="190" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="2:5" ht="339.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" ht="339.75" customHeight="1">
       <c r="B50" s="74" t="s">
         <v>80</v>
       </c>
       <c r="C50" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="D50" s="197" t="s">
+      <c r="D50" s="189" t="s">
         <v>82</v>
       </c>
-      <c r="E50" s="198" t="s">
+      <c r="E50" s="190" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="2:5" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" ht="84.75" customHeight="1">
       <c r="B51" s="74" t="s">
         <v>84</v>
       </c>
       <c r="C51" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="197" t="s">
+      <c r="D51" s="189" t="s">
         <v>86</v>
       </c>
-      <c r="E51" s="198" t="s">
+      <c r="E51" s="190" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="52" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" ht="90">
       <c r="B52" s="74" t="s">
         <v>87</v>
       </c>
       <c r="C52" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="D52" s="197"/>
-      <c r="E52" s="198"/>
-    </row>
-    <row r="53" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="D52" s="189"/>
+      <c r="E52" s="190"/>
+    </row>
+    <row r="53" spans="2:5" ht="75">
       <c r="B53" s="74" t="s">
         <v>89</v>
       </c>
       <c r="C53" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="D53" s="197"/>
-      <c r="E53" s="198"/>
-    </row>
-    <row r="54" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="D53" s="189"/>
+      <c r="E53" s="190"/>
+    </row>
+    <row r="54" spans="2:5" ht="45">
       <c r="B54" s="74" t="s">
         <v>91</v>
       </c>
       <c r="C54" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="D54" s="197"/>
-      <c r="E54" s="198"/>
-    </row>
-    <row r="55" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="D54" s="189"/>
+      <c r="E54" s="190"/>
+    </row>
+    <row r="55" spans="2:5" ht="75">
       <c r="B55" s="74" t="s">
         <v>93</v>
       </c>
       <c r="C55" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="D55" s="197"/>
-      <c r="E55" s="198"/>
-    </row>
-    <row r="56" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="D55" s="189"/>
+      <c r="E55" s="190"/>
+    </row>
+    <row r="56" spans="2:5" ht="75">
       <c r="B56" s="75" t="s">
         <v>95</v>
       </c>
       <c r="C56" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="D56" s="197"/>
-      <c r="E56" s="198"/>
-    </row>
-    <row r="57" spans="2:5" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D56" s="189"/>
+      <c r="E56" s="190"/>
+    </row>
+    <row r="57" spans="2:5" ht="37.5" customHeight="1" thickBot="1">
       <c r="B57" s="76" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="D57" s="199" t="s">
+      <c r="D57" s="171" t="s">
         <v>98</v>
       </c>
-      <c r="E57" s="200" t="s">
+      <c r="E57" s="172" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:5">
       <c r="B58" s="55"/>
       <c r="C58" s="55"/>
       <c r="D58" s="56"/>
       <c r="E58" s="56"/>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5">
       <c r="B59" s="57"/>
       <c r="C59" s="57"/>
       <c r="D59" s="56"/>
@@ -4746,6 +4770,44 @@
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
     <mergeCell ref="D57:E57"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B19:E19"/>
@@ -4762,44 +4824,6 @@
     <mergeCell ref="D56:E56"/>
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4812,8 +4836,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E74A078B-FDD5-4F89-B4CB-7471575D0D0F}">
-  <dimension ref="B1:Z84"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:Z86"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.28515625" style="9" customWidth="1"/>
     <col min="2" max="7" width="32.7109375" style="11" customWidth="1"/>
@@ -4833,7 +4857,7 @@
     <col min="27" max="16384" width="11.42578125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:26" ht="29.25" customHeight="1">
       <c r="B1" s="120"/>
       <c r="C1" s="147"/>
       <c r="D1" s="147"/>
@@ -4862,7 +4886,7 @@
       <c r="Y1" s="9"/>
       <c r="Z1" s="9"/>
     </row>
-    <row r="2" spans="2:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:26" ht="29.25" customHeight="1">
       <c r="B2" s="149"/>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -4891,15 +4915,15 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="172" t="s">
+    <row r="3" spans="2:26" ht="24" customHeight="1">
+      <c r="B3" s="199" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="174"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="201"/>
       <c r="H3" s="10"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
@@ -4920,15 +4944,15 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="175" t="s">
+    <row r="4" spans="2:26" ht="24" customHeight="1">
+      <c r="B4" s="202" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="176"/>
-      <c r="D4" s="176"/>
-      <c r="E4" s="176"/>
-      <c r="F4" s="176"/>
-      <c r="G4" s="177"/>
+      <c r="C4" s="203"/>
+      <c r="D4" s="203"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="203"/>
+      <c r="G4" s="204"/>
       <c r="H4" s="10"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -4949,15 +4973,15 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="172" t="s">
+    <row r="5" spans="2:26" ht="24" customHeight="1">
+      <c r="B5" s="199" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="174"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="200"/>
+      <c r="E5" s="200"/>
+      <c r="F5" s="200"/>
+      <c r="G5" s="201"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
       <c r="J5" s="9"/>
@@ -4978,15 +5002,15 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="175" t="s">
+    <row r="6" spans="2:26" ht="24" customHeight="1">
+      <c r="B6" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="176"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="177"/>
+      <c r="C6" s="203"/>
+      <c r="D6" s="203"/>
+      <c r="E6" s="203"/>
+      <c r="F6" s="203"/>
+      <c r="G6" s="204"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="9"/>
@@ -5007,15 +5031,15 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="172" t="s">
+    <row r="7" spans="2:26" ht="24" customHeight="1">
+      <c r="B7" s="199" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="173"/>
-      <c r="D7" s="173"/>
-      <c r="E7" s="173"/>
-      <c r="F7" s="173"/>
-      <c r="G7" s="174"/>
+      <c r="C7" s="200"/>
+      <c r="D7" s="200"/>
+      <c r="E7" s="200"/>
+      <c r="F7" s="200"/>
+      <c r="G7" s="201"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -5036,7 +5060,7 @@
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
     </row>
-    <row r="8" spans="2:26" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:26" ht="36.75" customHeight="1" thickBot="1">
       <c r="B8" s="151" t="s">
         <v>7</v>
       </c>
@@ -5069,7 +5093,7 @@
       <c r="Y8" s="9"/>
       <c r="Z8" s="9"/>
     </row>
-    <row r="9" spans="2:26" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:26" ht="9" customHeight="1" thickBot="1">
       <c r="B9" s="18"/>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -5096,7 +5120,7 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
     </row>
-    <row r="10" spans="2:26" s="11" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:26" s="11" customFormat="1" ht="29.25" customHeight="1">
       <c r="B10" s="120" t="s">
         <v>100</v>
       </c>
@@ -5116,7 +5140,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:26" ht="18" customHeight="1" thickBot="1">
       <c r="B11" s="115" t="s">
         <v>102</v>
       </c>
@@ -5155,7 +5179,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="2:26" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:26" ht="9" customHeight="1" thickBot="1">
       <c r="B12" s="20"/>
       <c r="D12" s="20"/>
       <c r="E12" s="18"/>
@@ -5181,7 +5205,7 @@
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
     </row>
-    <row r="13" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:26" ht="18" customHeight="1">
       <c r="B13" s="130" t="s">
         <v>106</v>
       </c>
@@ -5210,17 +5234,17 @@
       <c r="X13" s="18"/>
       <c r="Y13" s="18"/>
     </row>
-    <row r="14" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="218">
+    <row r="14" spans="2:26" ht="18" customHeight="1" thickBot="1">
+      <c r="B14" s="237">
         <v>2901692</v>
       </c>
-      <c r="C14" s="219"/>
-      <c r="D14" s="220"/>
-      <c r="E14" s="221" t="s">
+      <c r="C14" s="238"/>
+      <c r="D14" s="233"/>
+      <c r="E14" s="239" t="s">
         <v>107</v>
       </c>
-      <c r="F14" s="217"/>
-      <c r="G14" s="222"/>
+      <c r="F14" s="240"/>
+      <c r="G14" s="241"/>
       <c r="H14" s="20"/>
       <c r="I14" s="20"/>
       <c r="J14" s="20"/>
@@ -5239,7 +5263,7 @@
       <c r="X14" s="20"/>
       <c r="Y14" s="20"/>
     </row>
-    <row r="15" spans="2:26" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:26" ht="9.75" customHeight="1" thickBot="1">
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -5265,7 +5289,7 @@
       <c r="X15" s="15"/>
       <c r="Y15" s="15"/>
     </row>
-    <row r="16" spans="2:26" s="11" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:26" s="11" customFormat="1" ht="50.25" customHeight="1">
       <c r="B16" s="120" t="s">
         <v>108</v>
       </c>
@@ -5291,21 +5315,21 @@
       <c r="Y16" s="18"/>
       <c r="Z16" s="12"/>
     </row>
-    <row r="17" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="218" t="s">
+    <row r="17" spans="2:26" ht="18" customHeight="1" thickBot="1">
+      <c r="B17" s="237" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="220"/>
+      <c r="C17" s="233"/>
       <c r="D17" s="128">
         <v>901491551</v>
       </c>
       <c r="E17" s="129">
         <v>10</v>
       </c>
-      <c r="F17" s="223" t="s">
-        <v>202</v>
-      </c>
-      <c r="G17" s="224"/>
+      <c r="F17" s="242" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="243"/>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
       <c r="K17" s="20"/>
@@ -5316,7 +5340,7 @@
       <c r="X17" s="20"/>
       <c r="Y17" s="20"/>
     </row>
-    <row r="18" spans="2:26" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:26" ht="9.9499999999999993" customHeight="1" thickBot="1">
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -5342,7 +5366,7 @@
       <c r="X18" s="15"/>
       <c r="Y18" s="15"/>
     </row>
-    <row r="19" spans="2:26" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:26" s="11" customFormat="1" ht="45">
       <c r="B19" s="120" t="s">
         <v>53</v>
       </c>
@@ -5372,21 +5396,21 @@
       <c r="Y19" s="18"/>
       <c r="Z19" s="12"/>
     </row>
-    <row r="20" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="218" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="220"/>
+    <row r="20" spans="2:26" ht="18" customHeight="1">
+      <c r="B20" s="237" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="233"/>
       <c r="D20" s="161" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E20" s="124">
         <v>3104546105</v>
       </c>
-      <c r="F20" s="225" t="s">
-        <v>113</v>
-      </c>
-      <c r="G20" s="226"/>
+      <c r="F20" s="234" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" s="235"/>
       <c r="H20" s="20"/>
       <c r="L20" s="20"/>
       <c r="M20" s="20"/>
@@ -5401,7 +5425,7 @@
       <c r="X20" s="20"/>
       <c r="Y20" s="20"/>
     </row>
-    <row r="21" spans="2:26" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:26" ht="8.25" customHeight="1" thickBot="1">
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
@@ -5427,15 +5451,15 @@
       <c r="X21" s="15"/>
       <c r="Y21" s="15"/>
     </row>
-    <row r="22" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="233" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="234"/>
-      <c r="D22" s="234"/>
-      <c r="E22" s="234"/>
-      <c r="F22" s="234"/>
-      <c r="G22" s="235"/>
+    <row r="22" spans="2:26" ht="18" customHeight="1">
+      <c r="B22" s="223" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="224"/>
+      <c r="D22" s="224"/>
+      <c r="E22" s="224"/>
+      <c r="F22" s="224"/>
+      <c r="G22" s="225"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
@@ -5456,21 +5480,21 @@
       <c r="Y22" s="9"/>
       <c r="Z22" s="9"/>
     </row>
-    <row r="23" spans="2:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:26" ht="30" customHeight="1" thickBot="1">
       <c r="B23" s="155" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="242" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="220"/>
+      <c r="C23" s="232" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" s="233"/>
       <c r="E23" s="156" t="s">
-        <v>117</v>
-      </c>
-      <c r="F23" s="225" t="s">
         <v>118</v>
       </c>
-      <c r="G23" s="226"/>
+      <c r="F23" s="234" t="s">
+        <v>119</v>
+      </c>
+      <c r="G23" s="235"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
@@ -5491,7 +5515,7 @@
       <c r="Y23" s="9"/>
       <c r="Z23" s="9"/>
     </row>
-    <row r="24" spans="2:26" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:26" ht="9.9499999999999993" customHeight="1" thickBot="1">
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -5517,10 +5541,10 @@
       <c r="X24" s="15"/>
       <c r="Y24" s="15"/>
     </row>
-    <row r="25" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:26" ht="18" customHeight="1" thickBot="1">
       <c r="B25" s="38"/>
       <c r="C25" s="25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D25" s="38"/>
       <c r="E25" s="24"/>
@@ -5545,19 +5569,19 @@
       <c r="X25" s="23"/>
       <c r="Y25" s="23"/>
     </row>
-    <row r="26" spans="2:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:26" ht="30" customHeight="1" thickBot="1">
       <c r="B26" s="139" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C26" s="140" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D26" s="141"/>
       <c r="E26" s="142" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F26" s="140" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G26" s="140"/>
       <c r="H26" s="22"/>
@@ -5579,15 +5603,15 @@
       <c r="X26" s="23"/>
       <c r="Y26" s="23"/>
     </row>
-    <row r="27" spans="2:26" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:26" s="13" customFormat="1" ht="24.95" customHeight="1">
       <c r="B27" s="44"/>
       <c r="C27" s="81" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D27" s="82"/>
       <c r="E27" s="50"/>
       <c r="F27" s="81" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G27" s="83"/>
       <c r="H27" s="18"/>
@@ -5607,17 +5631,17 @@
       <c r="V27" s="20"/>
       <c r="Z27" s="14"/>
     </row>
-    <row r="28" spans="2:26" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:26" s="13" customFormat="1" ht="24.95" customHeight="1">
       <c r="B28" s="45"/>
       <c r="C28" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D28" s="40"/>
       <c r="E28" s="51"/>
-      <c r="F28" s="236" t="s">
-        <v>125</v>
-      </c>
-      <c r="G28" s="237"/>
+      <c r="F28" s="226" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" s="227"/>
       <c r="H28" s="18"/>
       <c r="I28" s="18"/>
       <c r="J28" s="20"/>
@@ -5635,17 +5659,17 @@
       <c r="V28" s="20"/>
       <c r="Z28" s="14"/>
     </row>
-    <row r="29" spans="2:26" s="13" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:26" s="13" customFormat="1" ht="34.5" customHeight="1">
       <c r="B29" s="46"/>
       <c r="C29" s="21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D29" s="40"/>
       <c r="E29" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="F29" s="236"/>
-      <c r="G29" s="237"/>
+        <v>128</v>
+      </c>
+      <c r="F29" s="226"/>
+      <c r="G29" s="227"/>
       <c r="H29" s="18"/>
       <c r="I29" s="18"/>
       <c r="J29" s="20"/>
@@ -5663,19 +5687,19 @@
       <c r="V29" s="20"/>
       <c r="Z29" s="14"/>
     </row>
-    <row r="30" spans="2:26" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:26" s="13" customFormat="1" ht="45" customHeight="1">
       <c r="B30" s="144" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D30" s="40"/>
       <c r="E30" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="18"/>
@@ -5695,15 +5719,15 @@
       <c r="V30" s="20"/>
       <c r="Z30" s="14"/>
     </row>
-    <row r="31" spans="2:26" s="13" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:26" s="13" customFormat="1" ht="45" customHeight="1" thickBot="1">
       <c r="B31" s="47"/>
       <c r="C31" s="21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D31" s="41"/>
       <c r="E31" s="45"/>
       <c r="F31" s="91" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G31" s="86"/>
       <c r="H31" s="18"/>
@@ -5726,18 +5750,18 @@
       <c r="Y31" s="15"/>
       <c r="Z31" s="14"/>
     </row>
-    <row r="32" spans="2:26" s="13" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:26" s="13" customFormat="1" ht="44.25" customHeight="1">
       <c r="B32" s="47"/>
       <c r="C32" s="21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D32" s="34"/>
       <c r="E32" s="49"/>
       <c r="F32" s="90" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G32" s="159" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
@@ -5759,17 +5783,17 @@
       <c r="Y32" s="15"/>
       <c r="Z32" s="14"/>
     </row>
-    <row r="33" spans="2:26" s="13" customFormat="1" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:26" s="13" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
       <c r="B33" s="48"/>
       <c r="C33" s="89" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D33" s="145"/>
       <c r="E33" s="87" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G33" s="39"/>
       <c r="H33" s="18"/>
@@ -5792,15 +5816,15 @@
       <c r="Y33" s="15"/>
       <c r="Z33" s="14"/>
     </row>
-    <row r="34" spans="2:26" s="13" customFormat="1" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:26" s="13" customFormat="1" ht="45.6" customHeight="1" thickBot="1">
       <c r="B34" s="49"/>
       <c r="C34" s="90" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D34" s="146"/>
       <c r="E34" s="53"/>
       <c r="F34" s="85" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G34" s="86"/>
       <c r="H34" s="18"/>
@@ -5823,19 +5847,19 @@
       <c r="Y34" s="15"/>
       <c r="Z34" s="14"/>
     </row>
-    <row r="35" spans="2:26" s="13" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:26" s="13" customFormat="1" ht="31.5" customHeight="1">
       <c r="B35" s="46" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D35" s="40"/>
       <c r="E35" s="87" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F35" s="88" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G35" s="92"/>
       <c r="H35" s="18"/>
@@ -5858,15 +5882,15 @@
       <c r="Y35" s="15"/>
       <c r="Z35" s="14"/>
     </row>
-    <row r="36" spans="2:26" s="13" customFormat="1" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:26" s="13" customFormat="1" ht="46.5" customHeight="1" thickBot="1">
       <c r="B36" s="48"/>
       <c r="C36" s="84" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D36" s="86"/>
       <c r="E36" s="143"/>
       <c r="F36" s="85" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G36" s="86"/>
       <c r="H36" s="18"/>
@@ -5889,7 +5913,7 @@
       <c r="Y36" s="15"/>
       <c r="Z36" s="14"/>
     </row>
-    <row r="37" spans="2:26" s="13" customFormat="1" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:26" s="13" customFormat="1" ht="9.75" customHeight="1" thickBot="1">
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
       <c r="J37" s="19"/>
@@ -5910,24 +5934,24 @@
       <c r="Y37" s="15"/>
       <c r="Z37" s="14"/>
     </row>
-    <row r="38" spans="2:26" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:26" ht="68.25" customHeight="1">
       <c r="B38" s="93" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C38" s="94" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D38" s="95" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E38" s="95" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F38" s="95" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G38" s="96" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
@@ -5948,20 +5972,20 @@
       <c r="X38" s="18"/>
       <c r="Y38" s="18"/>
     </row>
-    <row r="39" spans="2:26" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:26" ht="52.5" customHeight="1">
       <c r="B39" s="163" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C39" s="164" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D39" s="165"/>
       <c r="E39" s="165"/>
       <c r="F39" s="166" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G39" s="167" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
@@ -5982,22 +6006,22 @@
       <c r="X39" s="18"/>
       <c r="Y39" s="18"/>
     </row>
-    <row r="40" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="213" t="s">
-        <v>203</v>
-      </c>
-      <c r="C40" s="213"/>
-      <c r="D40" s="214">
+    <row r="40" spans="2:26" ht="15" customHeight="1">
+      <c r="B40" s="216" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" s="216"/>
+      <c r="D40" s="236">
         <v>46070</v>
       </c>
-      <c r="E40" s="214">
+      <c r="E40" s="236">
         <v>46070</v>
       </c>
-      <c r="F40" s="214" t="s">
-        <v>213</v>
-      </c>
-      <c r="G40" s="214" t="s">
-        <v>223</v>
+      <c r="F40" s="236" t="s">
+        <v>160</v>
+      </c>
+      <c r="G40" s="236" t="s">
+        <v>161</v>
       </c>
       <c r="H40" s="20"/>
       <c r="I40" s="18"/>
@@ -6018,13 +6042,13 @@
       <c r="X40" s="18"/>
       <c r="Y40" s="18"/>
     </row>
-    <row r="41" spans="2:26" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="213"/>
-      <c r="C41" s="213"/>
-      <c r="D41" s="213"/>
-      <c r="E41" s="213"/>
-      <c r="F41" s="213"/>
-      <c r="G41" s="213"/>
+    <row r="41" spans="2:26" ht="41.25" customHeight="1">
+      <c r="B41" s="216"/>
+      <c r="C41" s="216"/>
+      <c r="D41" s="216"/>
+      <c r="E41" s="216"/>
+      <c r="F41" s="216"/>
+      <c r="G41" s="216"/>
       <c r="H41" s="20"/>
       <c r="I41" s="18"/>
       <c r="J41" s="18"/>
@@ -6044,22 +6068,22 @@
       <c r="X41" s="18"/>
       <c r="Y41" s="18"/>
     </row>
-    <row r="42" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="213" t="s">
-        <v>206</v>
-      </c>
-      <c r="C42" s="213"/>
-      <c r="D42" s="214">
+    <row r="42" spans="2:26" ht="15" customHeight="1">
+      <c r="B42" s="216" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="216"/>
+      <c r="D42" s="236">
         <v>46071</v>
       </c>
-      <c r="E42" s="214">
+      <c r="E42" s="236">
         <v>46071</v>
       </c>
-      <c r="F42" s="214" t="s">
-        <v>216</v>
-      </c>
-      <c r="G42" s="214" t="s">
-        <v>224</v>
+      <c r="F42" s="236" t="s">
+        <v>163</v>
+      </c>
+      <c r="G42" s="236" t="s">
+        <v>164</v>
       </c>
       <c r="H42" s="20"/>
       <c r="I42" s="18"/>
@@ -6080,13 +6104,13 @@
       <c r="X42" s="18"/>
       <c r="Y42" s="18"/>
     </row>
-    <row r="43" spans="2:26" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="213"/>
-      <c r="C43" s="213"/>
-      <c r="D43" s="213"/>
-      <c r="E43" s="213"/>
-      <c r="F43" s="213"/>
-      <c r="G43" s="213"/>
+    <row r="43" spans="2:26" ht="51.75" customHeight="1">
+      <c r="B43" s="216"/>
+      <c r="C43" s="216"/>
+      <c r="D43" s="216"/>
+      <c r="E43" s="216"/>
+      <c r="F43" s="216"/>
+      <c r="G43" s="216"/>
       <c r="H43" s="20"/>
       <c r="I43" s="18"/>
       <c r="J43" s="18"/>
@@ -6106,22 +6130,22 @@
       <c r="X43" s="18"/>
       <c r="Y43" s="18"/>
     </row>
-    <row r="44" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="213" t="s">
-        <v>204</v>
-      </c>
-      <c r="C44" s="213"/>
-      <c r="D44" s="214">
+    <row r="44" spans="2:26" ht="15" customHeight="1">
+      <c r="B44" s="216" t="s">
+        <v>165</v>
+      </c>
+      <c r="C44" s="216"/>
+      <c r="D44" s="236">
         <v>46071</v>
       </c>
-      <c r="E44" s="214">
+      <c r="E44" s="236">
         <v>46071</v>
       </c>
-      <c r="F44" s="214" t="s">
-        <v>214</v>
-      </c>
-      <c r="G44" s="214" t="s">
-        <v>225</v>
+      <c r="F44" s="236" t="s">
+        <v>166</v>
+      </c>
+      <c r="G44" s="236" t="s">
+        <v>167</v>
       </c>
       <c r="H44" s="20"/>
       <c r="I44" s="18"/>
@@ -6142,13 +6166,13 @@
       <c r="X44" s="18"/>
       <c r="Y44" s="18"/>
     </row>
-    <row r="45" spans="2:26" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="213"/>
-      <c r="C45" s="213"/>
-      <c r="D45" s="213"/>
-      <c r="E45" s="213"/>
-      <c r="F45" s="213"/>
-      <c r="G45" s="213"/>
+    <row r="45" spans="2:26" ht="51.75" customHeight="1">
+      <c r="B45" s="216"/>
+      <c r="C45" s="216"/>
+      <c r="D45" s="216"/>
+      <c r="E45" s="216"/>
+      <c r="F45" s="216"/>
+      <c r="G45" s="216"/>
       <c r="H45" s="20"/>
       <c r="I45" s="18"/>
       <c r="J45" s="18"/>
@@ -6168,22 +6192,22 @@
       <c r="X45" s="18"/>
       <c r="Y45" s="18"/>
     </row>
-    <row r="46" spans="2:26" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="213" t="s">
-        <v>205</v>
-      </c>
-      <c r="C46" s="213"/>
-      <c r="D46" s="214">
+    <row r="46" spans="2:26" ht="77.25" customHeight="1">
+      <c r="B46" s="216" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="216"/>
+      <c r="D46" s="236">
         <v>46070</v>
       </c>
-      <c r="E46" s="214">
+      <c r="E46" s="236">
         <v>46070</v>
       </c>
-      <c r="F46" s="214" t="s">
-        <v>215</v>
-      </c>
-      <c r="G46" s="214" t="s">
-        <v>226</v>
+      <c r="F46" s="236" t="s">
+        <v>169</v>
+      </c>
+      <c r="G46" s="236" t="s">
+        <v>170</v>
       </c>
       <c r="H46" s="20"/>
       <c r="I46" s="18"/>
@@ -6204,13 +6228,13 @@
       <c r="X46" s="18"/>
       <c r="Y46" s="18"/>
     </row>
-    <row r="47" spans="2:26" ht="52.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="213"/>
-      <c r="C47" s="213"/>
-      <c r="D47" s="213"/>
-      <c r="E47" s="213"/>
-      <c r="F47" s="213"/>
-      <c r="G47" s="213"/>
+    <row r="47" spans="2:26" ht="52.5" hidden="1" customHeight="1">
+      <c r="B47" s="216"/>
+      <c r="C47" s="216"/>
+      <c r="D47" s="216"/>
+      <c r="E47" s="216"/>
+      <c r="F47" s="216"/>
+      <c r="G47" s="216"/>
       <c r="H47" s="20"/>
       <c r="I47" s="18"/>
       <c r="J47" s="18"/>
@@ -6230,22 +6254,22 @@
       <c r="X47" s="18"/>
       <c r="Y47" s="18"/>
     </row>
-    <row r="48" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="213" t="s">
-        <v>207</v>
-      </c>
-      <c r="C48" s="213"/>
-      <c r="D48" s="215">
+    <row r="48" spans="2:26" ht="15" customHeight="1">
+      <c r="B48" s="216" t="s">
+        <v>171</v>
+      </c>
+      <c r="C48" s="216"/>
+      <c r="D48" s="244">
         <v>46070</v>
       </c>
-      <c r="E48" s="215">
+      <c r="E48" s="244">
         <v>46070</v>
       </c>
-      <c r="F48" s="213" t="s">
-        <v>217</v>
-      </c>
-      <c r="G48" s="213" t="s">
-        <v>227</v>
+      <c r="F48" s="216" t="s">
+        <v>172</v>
+      </c>
+      <c r="G48" s="216" t="s">
+        <v>173</v>
       </c>
       <c r="H48" s="20"/>
       <c r="I48" s="18"/>
@@ -6266,13 +6290,13 @@
       <c r="X48" s="18"/>
       <c r="Y48" s="18"/>
     </row>
-    <row r="49" spans="2:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="213"/>
-      <c r="C49" s="213"/>
-      <c r="D49" s="213"/>
-      <c r="E49" s="213"/>
-      <c r="F49" s="213"/>
-      <c r="G49" s="213"/>
+    <row r="49" spans="2:25" ht="48.75" customHeight="1">
+      <c r="B49" s="216"/>
+      <c r="C49" s="216"/>
+      <c r="D49" s="216"/>
+      <c r="E49" s="216"/>
+      <c r="F49" s="216"/>
+      <c r="G49" s="216"/>
       <c r="H49" s="20"/>
       <c r="I49" s="18"/>
       <c r="J49" s="18"/>
@@ -6292,22 +6316,22 @@
       <c r="X49" s="18"/>
       <c r="Y49" s="18"/>
     </row>
-    <row r="50" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="213" t="s">
-        <v>208</v>
-      </c>
-      <c r="C50" s="213"/>
-      <c r="D50" s="215">
+    <row r="50" spans="2:25" ht="15" customHeight="1">
+      <c r="B50" s="216" t="s">
+        <v>174</v>
+      </c>
+      <c r="C50" s="216"/>
+      <c r="D50" s="244">
         <v>46071</v>
       </c>
-      <c r="E50" s="215">
+      <c r="E50" s="244">
         <v>46071</v>
       </c>
-      <c r="F50" s="213" t="s">
-        <v>218</v>
-      </c>
-      <c r="G50" s="213" t="s">
-        <v>228</v>
+      <c r="F50" s="216" t="s">
+        <v>175</v>
+      </c>
+      <c r="G50" s="216" t="s">
+        <v>176</v>
       </c>
       <c r="H50" s="20"/>
       <c r="I50" s="18"/>
@@ -6328,13 +6352,13 @@
       <c r="X50" s="18"/>
       <c r="Y50" s="18"/>
     </row>
-    <row r="51" spans="2:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="213"/>
-      <c r="C51" s="213"/>
-      <c r="D51" s="213"/>
-      <c r="E51" s="213"/>
-      <c r="F51" s="213"/>
-      <c r="G51" s="213"/>
+    <row r="51" spans="2:25" ht="32.25" customHeight="1">
+      <c r="B51" s="216"/>
+      <c r="C51" s="216"/>
+      <c r="D51" s="216"/>
+      <c r="E51" s="216"/>
+      <c r="F51" s="216"/>
+      <c r="G51" s="216"/>
       <c r="H51" s="20"/>
       <c r="I51" s="18"/>
       <c r="J51" s="18"/>
@@ -6354,22 +6378,22 @@
       <c r="X51" s="18"/>
       <c r="Y51" s="18"/>
     </row>
-    <row r="52" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="213" t="s">
-        <v>209</v>
-      </c>
-      <c r="C52" s="213"/>
-      <c r="D52" s="215">
+    <row r="52" spans="2:25" ht="15" customHeight="1">
+      <c r="B52" s="216" t="s">
+        <v>177</v>
+      </c>
+      <c r="C52" s="216"/>
+      <c r="D52" s="244">
         <v>46071</v>
       </c>
-      <c r="E52" s="215">
+      <c r="E52" s="244">
         <v>46071</v>
       </c>
-      <c r="F52" s="213" t="s">
-        <v>219</v>
-      </c>
-      <c r="G52" s="213" t="s">
-        <v>229</v>
+      <c r="F52" s="216" t="s">
+        <v>178</v>
+      </c>
+      <c r="G52" s="216" t="s">
+        <v>179</v>
       </c>
       <c r="H52" s="20"/>
       <c r="I52" s="18"/>
@@ -6390,13 +6414,13 @@
       <c r="X52" s="18"/>
       <c r="Y52" s="18"/>
     </row>
-    <row r="53" spans="2:25" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="213"/>
-      <c r="C53" s="213"/>
-      <c r="D53" s="213"/>
-      <c r="E53" s="213"/>
-      <c r="F53" s="213"/>
-      <c r="G53" s="213"/>
+    <row r="53" spans="2:25" ht="40.5" customHeight="1">
+      <c r="B53" s="216"/>
+      <c r="C53" s="216"/>
+      <c r="D53" s="216"/>
+      <c r="E53" s="216"/>
+      <c r="F53" s="216"/>
+      <c r="G53" s="216"/>
       <c r="H53" s="20"/>
       <c r="I53" s="18"/>
       <c r="J53" s="18"/>
@@ -6416,22 +6440,22 @@
       <c r="X53" s="18"/>
       <c r="Y53" s="18"/>
     </row>
-    <row r="54" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="213" t="s">
-        <v>210</v>
-      </c>
-      <c r="C54" s="213"/>
-      <c r="D54" s="215">
+    <row r="54" spans="2:25" ht="15" customHeight="1">
+      <c r="B54" s="216" t="s">
+        <v>180</v>
+      </c>
+      <c r="C54" s="216"/>
+      <c r="D54" s="244">
         <v>46076</v>
       </c>
-      <c r="E54" s="215">
+      <c r="E54" s="244">
         <v>46076</v>
       </c>
-      <c r="F54" s="213" t="s">
-        <v>220</v>
-      </c>
-      <c r="G54" s="213" t="s">
-        <v>230</v>
+      <c r="F54" s="216" t="s">
+        <v>181</v>
+      </c>
+      <c r="G54" s="216" t="s">
+        <v>182</v>
       </c>
       <c r="H54" s="20"/>
       <c r="I54" s="18"/>
@@ -6452,13 +6476,13 @@
       <c r="X54" s="18"/>
       <c r="Y54" s="18"/>
     </row>
-    <row r="55" spans="2:25" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="213"/>
-      <c r="C55" s="213"/>
-      <c r="D55" s="213"/>
-      <c r="E55" s="213"/>
-      <c r="F55" s="213"/>
-      <c r="G55" s="213"/>
+    <row r="55" spans="2:25" ht="27" customHeight="1">
+      <c r="B55" s="216"/>
+      <c r="C55" s="216"/>
+      <c r="D55" s="216"/>
+      <c r="E55" s="216"/>
+      <c r="F55" s="216"/>
+      <c r="G55" s="216"/>
       <c r="H55" s="20"/>
       <c r="I55" s="18"/>
       <c r="J55" s="18"/>
@@ -6478,22 +6502,22 @@
       <c r="X55" s="18"/>
       <c r="Y55" s="18"/>
     </row>
-    <row r="56" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="213" t="s">
-        <v>211</v>
-      </c>
-      <c r="C56" s="213"/>
-      <c r="D56" s="214">
+    <row r="56" spans="2:25" ht="15" customHeight="1">
+      <c r="B56" s="216" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" s="216"/>
+      <c r="D56" s="236">
         <v>46077</v>
       </c>
-      <c r="E56" s="214">
+      <c r="E56" s="236">
         <v>46077</v>
       </c>
-      <c r="F56" s="213" t="s">
-        <v>221</v>
-      </c>
-      <c r="G56" s="213" t="s">
-        <v>223</v>
+      <c r="F56" s="216" t="s">
+        <v>184</v>
+      </c>
+      <c r="G56" s="216" t="s">
+        <v>161</v>
       </c>
       <c r="H56" s="20"/>
       <c r="I56" s="18"/>
@@ -6514,13 +6538,13 @@
       <c r="X56" s="18"/>
       <c r="Y56" s="18"/>
     </row>
-    <row r="57" spans="2:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="213"/>
-      <c r="C57" s="213"/>
-      <c r="D57" s="213"/>
-      <c r="E57" s="213"/>
-      <c r="F57" s="213"/>
-      <c r="G57" s="213"/>
+    <row r="57" spans="2:25" ht="28.5" customHeight="1">
+      <c r="B57" s="216"/>
+      <c r="C57" s="216"/>
+      <c r="D57" s="216"/>
+      <c r="E57" s="216"/>
+      <c r="F57" s="216"/>
+      <c r="G57" s="216"/>
       <c r="H57" s="20"/>
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
@@ -6540,22 +6564,22 @@
       <c r="X57" s="18"/>
       <c r="Y57" s="18"/>
     </row>
-    <row r="58" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="213" t="s">
-        <v>212</v>
-      </c>
-      <c r="C58" s="213"/>
-      <c r="D58" s="214">
+    <row r="58" spans="2:25" ht="15" customHeight="1">
+      <c r="B58" s="216" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58" s="216"/>
+      <c r="D58" s="236">
         <v>46078</v>
       </c>
-      <c r="E58" s="214">
+      <c r="E58" s="236">
         <v>46078</v>
       </c>
-      <c r="F58" s="213" t="s">
-        <v>222</v>
-      </c>
-      <c r="G58" s="213" t="s">
-        <v>231</v>
+      <c r="F58" s="216" t="s">
+        <v>186</v>
+      </c>
+      <c r="G58" s="216" t="s">
+        <v>187</v>
       </c>
       <c r="H58" s="20"/>
       <c r="I58" s="18"/>
@@ -6576,13 +6600,13 @@
       <c r="X58" s="18"/>
       <c r="Y58" s="18"/>
     </row>
-    <row r="59" spans="2:25" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="213"/>
-      <c r="C59" s="213"/>
-      <c r="D59" s="213"/>
-      <c r="E59" s="213"/>
-      <c r="F59" s="213"/>
-      <c r="G59" s="213"/>
+    <row r="59" spans="2:25" ht="41.25" customHeight="1">
+      <c r="B59" s="216"/>
+      <c r="C59" s="216"/>
+      <c r="D59" s="216"/>
+      <c r="E59" s="216"/>
+      <c r="F59" s="216"/>
+      <c r="G59" s="216"/>
       <c r="H59" s="20"/>
       <c r="I59" s="18"/>
       <c r="J59" s="18"/>
@@ -6602,13 +6626,23 @@
       <c r="X59" s="18"/>
       <c r="Y59" s="18"/>
     </row>
-    <row r="60" spans="2:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="27"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
+    <row r="60" spans="2:25" ht="57" customHeight="1">
+      <c r="B60" s="246" t="s">
+        <v>188</v>
+      </c>
+      <c r="C60" s="247"/>
+      <c r="D60" s="169">
+        <v>46068</v>
+      </c>
+      <c r="E60" s="169">
+        <v>46081</v>
+      </c>
+      <c r="F60" s="168" t="s">
+        <v>189</v>
+      </c>
+      <c r="G60" s="168" t="s">
+        <v>190</v>
+      </c>
       <c r="H60" s="20"/>
       <c r="I60" s="18"/>
       <c r="J60" s="18"/>
@@ -6628,127 +6662,123 @@
       <c r="X60" s="18"/>
       <c r="Y60" s="18"/>
     </row>
-    <row r="61" spans="2:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="97"/>
-      <c r="C61" s="98" t="s">
-        <v>158</v>
-      </c>
-      <c r="D61" s="99"/>
-      <c r="E61" s="99"/>
-      <c r="F61" s="99"/>
-      <c r="G61" s="100"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="22"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="22"/>
-      <c r="R61" s="22"/>
-      <c r="S61" s="22"/>
-      <c r="T61" s="22"/>
-      <c r="U61" s="22"/>
-      <c r="V61" s="22"/>
-      <c r="W61" s="22"/>
-      <c r="X61" s="22"/>
-      <c r="Y61" s="22"/>
-    </row>
-    <row r="62" spans="2:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="239" t="s">
-        <v>159</v>
-      </c>
-      <c r="C62" s="240"/>
-      <c r="D62" s="240"/>
-      <c r="E62" s="240"/>
-      <c r="F62" s="240"/>
-      <c r="G62" s="241"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="22"/>
-      <c r="K62" s="22"/>
-      <c r="L62" s="22"/>
-      <c r="M62" s="22"/>
-      <c r="N62" s="22"/>
-      <c r="O62" s="22"/>
-      <c r="P62" s="22"/>
-      <c r="Q62" s="22"/>
-      <c r="R62" s="22"/>
-      <c r="S62" s="22"/>
-      <c r="T62" s="22"/>
-      <c r="U62" s="22"/>
-      <c r="V62" s="22"/>
-      <c r="W62" s="22"/>
-      <c r="X62" s="22"/>
-      <c r="Y62" s="22"/>
-    </row>
-    <row r="63" spans="2:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="101" t="s">
-        <v>160</v>
-      </c>
-      <c r="C63" s="28"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="102"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="29"/>
-      <c r="J63" s="29"/>
-      <c r="K63" s="29"/>
-      <c r="L63" s="29"/>
-      <c r="M63" s="29"/>
-      <c r="N63" s="29"/>
-      <c r="O63" s="29"/>
-      <c r="P63" s="29"/>
-      <c r="Q63" s="29"/>
-      <c r="R63" s="29"/>
-      <c r="S63" s="29"/>
-      <c r="T63" s="29"/>
-      <c r="U63" s="29"/>
-      <c r="V63" s="29"/>
-      <c r="W63" s="29"/>
-      <c r="X63" s="29"/>
-      <c r="Y63" s="29"/>
-    </row>
-    <row r="64" spans="2:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="103" t="s">
-        <v>161</v>
-      </c>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="104"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-      <c r="T64" s="29"/>
-      <c r="U64" s="29"/>
-      <c r="V64" s="29"/>
-      <c r="W64" s="29"/>
-      <c r="X64" s="29"/>
-      <c r="Y64" s="29"/>
-    </row>
-    <row r="65" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="103" t="s">
-        <v>162</v>
-      </c>
-      <c r="C65" s="29"/>
-      <c r="D65" s="29"/>
-      <c r="E65" s="29"/>
-      <c r="F65" s="29"/>
-      <c r="G65" s="104"/>
+    <row r="61" spans="2:25" ht="19.5" customHeight="1">
+      <c r="B61" s="170"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="18"/>
+      <c r="L61" s="18"/>
+      <c r="M61" s="18"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="18"/>
+      <c r="P61" s="18"/>
+      <c r="Q61" s="18"/>
+      <c r="R61" s="18"/>
+      <c r="S61" s="18"/>
+      <c r="T61" s="18"/>
+      <c r="U61" s="18"/>
+      <c r="V61" s="18"/>
+      <c r="W61" s="18"/>
+      <c r="X61" s="18"/>
+      <c r="Y61" s="18"/>
+    </row>
+    <row r="62" spans="2:25" ht="15" customHeight="1" thickBot="1">
+      <c r="B62" s="27"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
+      <c r="P62" s="18"/>
+      <c r="Q62" s="18"/>
+      <c r="R62" s="18"/>
+      <c r="S62" s="18"/>
+      <c r="T62" s="18"/>
+      <c r="U62" s="18"/>
+      <c r="V62" s="18"/>
+      <c r="W62" s="18"/>
+      <c r="X62" s="18"/>
+      <c r="Y62" s="18"/>
+    </row>
+    <row r="63" spans="2:25" ht="23.25" customHeight="1">
+      <c r="B63" s="97"/>
+      <c r="C63" s="98" t="s">
+        <v>191</v>
+      </c>
+      <c r="D63" s="99"/>
+      <c r="E63" s="99"/>
+      <c r="F63" s="99"/>
+      <c r="G63" s="100"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="22"/>
+      <c r="K63" s="22"/>
+      <c r="L63" s="22"/>
+      <c r="M63" s="22"/>
+      <c r="N63" s="22"/>
+      <c r="O63" s="22"/>
+      <c r="P63" s="22"/>
+      <c r="Q63" s="22"/>
+      <c r="R63" s="22"/>
+      <c r="S63" s="22"/>
+      <c r="T63" s="22"/>
+      <c r="U63" s="22"/>
+      <c r="V63" s="22"/>
+      <c r="W63" s="22"/>
+      <c r="X63" s="22"/>
+      <c r="Y63" s="22"/>
+    </row>
+    <row r="64" spans="2:25" ht="19.5" customHeight="1">
+      <c r="B64" s="229" t="s">
+        <v>192</v>
+      </c>
+      <c r="C64" s="230"/>
+      <c r="D64" s="230"/>
+      <c r="E64" s="230"/>
+      <c r="F64" s="230"/>
+      <c r="G64" s="231"/>
+      <c r="H64" s="22"/>
+      <c r="I64" s="22"/>
+      <c r="J64" s="22"/>
+      <c r="K64" s="22"/>
+      <c r="L64" s="22"/>
+      <c r="M64" s="22"/>
+      <c r="N64" s="22"/>
+      <c r="O64" s="22"/>
+      <c r="P64" s="22"/>
+      <c r="Q64" s="22"/>
+      <c r="R64" s="22"/>
+      <c r="S64" s="22"/>
+      <c r="T64" s="22"/>
+      <c r="U64" s="22"/>
+      <c r="V64" s="22"/>
+      <c r="W64" s="22"/>
+      <c r="X64" s="22"/>
+      <c r="Y64" s="22"/>
+    </row>
+    <row r="65" spans="2:26" ht="16.5" customHeight="1">
+      <c r="B65" s="101" t="s">
+        <v>193</v>
+      </c>
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="102"/>
       <c r="H65" s="29"/>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
@@ -6768,9 +6798,9 @@
       <c r="X65" s="29"/>
       <c r="Y65" s="29"/>
     </row>
-    <row r="66" spans="2:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:26" ht="16.5" customHeight="1">
       <c r="B66" s="103" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="C66" s="29"/>
       <c r="D66" s="29"/>
@@ -6796,83 +6826,81 @@
       <c r="X66" s="29"/>
       <c r="Y66" s="29"/>
     </row>
-    <row r="67" spans="2:26" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="110" t="s">
+    <row r="67" spans="2:26" ht="16.5" customHeight="1">
+      <c r="B67" s="103" t="s">
+        <v>195</v>
+      </c>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="104"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="29"/>
+      <c r="L67" s="29"/>
+      <c r="M67" s="29"/>
+      <c r="N67" s="29"/>
+      <c r="O67" s="29"/>
+      <c r="P67" s="29"/>
+      <c r="Q67" s="29"/>
+      <c r="R67" s="29"/>
+      <c r="S67" s="29"/>
+      <c r="T67" s="29"/>
+      <c r="U67" s="29"/>
+      <c r="V67" s="29"/>
+      <c r="W67" s="29"/>
+      <c r="X67" s="29"/>
+      <c r="Y67" s="29"/>
+    </row>
+    <row r="68" spans="2:26" ht="16.5" customHeight="1" thickBot="1">
+      <c r="B68" s="103" t="s">
+        <v>196</v>
+      </c>
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
+      <c r="E68" s="29"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="104"/>
+      <c r="H68" s="29"/>
+      <c r="I68" s="29"/>
+      <c r="J68" s="29"/>
+      <c r="K68" s="29"/>
+      <c r="L68" s="29"/>
+      <c r="M68" s="29"/>
+      <c r="N68" s="29"/>
+      <c r="O68" s="29"/>
+      <c r="P68" s="29"/>
+      <c r="Q68" s="29"/>
+      <c r="R68" s="29"/>
+      <c r="S68" s="29"/>
+      <c r="T68" s="29"/>
+      <c r="U68" s="29"/>
+      <c r="V68" s="29"/>
+      <c r="W68" s="29"/>
+      <c r="X68" s="29"/>
+      <c r="Y68" s="29"/>
+    </row>
+    <row r="69" spans="2:26" ht="79.5" customHeight="1">
+      <c r="B69" s="110" t="s">
         <v>77</v>
       </c>
-      <c r="C67" s="111" t="s">
+      <c r="C69" s="111" t="s">
         <v>80</v>
       </c>
-      <c r="D67" s="112" t="s">
+      <c r="D69" s="112" t="s">
         <v>84</v>
       </c>
-      <c r="E67" s="113" t="s">
-        <v>164</v>
-      </c>
-      <c r="F67" s="112" t="s">
-        <v>165</v>
-      </c>
-      <c r="G67" s="114" t="s">
-        <v>164</v>
-      </c>
-      <c r="H67" s="18"/>
-      <c r="I67" s="18"/>
-      <c r="J67" s="18"/>
-      <c r="K67" s="18"/>
-      <c r="L67" s="18"/>
-      <c r="M67" s="18"/>
-      <c r="N67" s="18"/>
-      <c r="O67" s="18"/>
-      <c r="P67" s="18"/>
-      <c r="Q67" s="18"/>
-      <c r="R67" s="18"/>
-      <c r="S67" s="18"/>
-      <c r="T67" s="18"/>
-      <c r="U67" s="18"/>
-      <c r="V67" s="18"/>
-      <c r="W67" s="18"/>
-      <c r="X67" s="18"/>
-      <c r="Y67" s="18"/>
-      <c r="Z67" s="18"/>
-    </row>
-    <row r="68" spans="2:26" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="105" t="s">
-        <v>166</v>
-      </c>
-      <c r="C68" s="106">
-        <v>1</v>
-      </c>
-      <c r="D68" s="107"/>
-      <c r="E68" s="108"/>
-      <c r="F68" s="107"/>
-      <c r="G68" s="109"/>
-      <c r="H68" s="18"/>
-      <c r="I68" s="18"/>
-      <c r="J68" s="18"/>
-      <c r="K68" s="18"/>
-      <c r="L68" s="18"/>
-      <c r="M68" s="18"/>
-      <c r="N68" s="18"/>
-      <c r="O68" s="18"/>
-      <c r="P68" s="18"/>
-      <c r="Q68" s="18"/>
-      <c r="R68" s="18"/>
-      <c r="S68" s="18"/>
-      <c r="T68" s="18"/>
-      <c r="U68" s="18"/>
-      <c r="V68" s="18"/>
-      <c r="W68" s="18"/>
-      <c r="X68" s="18"/>
-      <c r="Y68" s="18"/>
-      <c r="Z68" s="18"/>
-    </row>
-    <row r="69" spans="2:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
+      <c r="E69" s="113" t="s">
+        <v>197</v>
+      </c>
+      <c r="F69" s="112" t="s">
+        <v>198</v>
+      </c>
+      <c r="G69" s="114" t="s">
+        <v>197</v>
+      </c>
       <c r="H69" s="18"/>
       <c r="I69" s="18"/>
       <c r="J69" s="18"/>
@@ -6893,14 +6921,17 @@
       <c r="Y69" s="18"/>
       <c r="Z69" s="18"/>
     </row>
-    <row r="70" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="30"/>
-      <c r="D70" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
+    <row r="70" spans="2:26" ht="32.25" customHeight="1" thickBot="1">
+      <c r="B70" s="105" t="s">
+        <v>199</v>
+      </c>
+      <c r="C70" s="106">
+        <v>1</v>
+      </c>
+      <c r="D70" s="107"/>
+      <c r="E70" s="108"/>
+      <c r="F70" s="107"/>
+      <c r="G70" s="109"/>
       <c r="H70" s="18"/>
       <c r="I70" s="18"/>
       <c r="J70" s="18"/>
@@ -6921,13 +6952,13 @@
       <c r="Y70" s="18"/>
       <c r="Z70" s="18"/>
     </row>
-    <row r="71" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="17"/>
-      <c r="G71" s="17"/>
+    <row r="71" spans="2:26" ht="17.25" customHeight="1">
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
       <c r="H71" s="18"/>
       <c r="I71" s="18"/>
       <c r="J71" s="18"/>
@@ -6948,13 +6979,14 @@
       <c r="Y71" s="18"/>
       <c r="Z71" s="18"/>
     </row>
-    <row r="72" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="17"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="17"/>
-      <c r="G72" s="17"/>
+    <row r="72" spans="2:26" ht="15" customHeight="1">
+      <c r="C72" s="30"/>
+      <c r="D72" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
       <c r="H72" s="18"/>
       <c r="I72" s="18"/>
       <c r="J72" s="18"/>
@@ -6975,14 +7007,13 @@
       <c r="Y72" s="18"/>
       <c r="Z72" s="18"/>
     </row>
-    <row r="73" spans="2:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="216"/>
-      <c r="C73" s="216"/>
-      <c r="D73" s="216"/>
-      <c r="F73" s="160">
-        <v>46021</v>
-      </c>
-      <c r="G73" s="18"/>
+    <row r="73" spans="2:26" ht="15" customHeight="1">
+      <c r="B73" s="17"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="17"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="17"/>
+      <c r="G73" s="17"/>
       <c r="H73" s="18"/>
       <c r="I73" s="18"/>
       <c r="J73" s="18"/>
@@ -7003,16 +7034,13 @@
       <c r="Y73" s="18"/>
       <c r="Z73" s="18"/>
     </row>
-    <row r="74" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="238" t="s">
-        <v>89</v>
-      </c>
-      <c r="C74" s="238"/>
-      <c r="D74" s="238"/>
-      <c r="F74" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="G74" s="18"/>
+    <row r="74" spans="2:26" ht="15" customHeight="1">
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="17"/>
+      <c r="G74" s="17"/>
       <c r="H74" s="18"/>
       <c r="I74" s="18"/>
       <c r="J74" s="18"/>
@@ -7033,11 +7061,13 @@
       <c r="Y74" s="18"/>
       <c r="Z74" s="18"/>
     </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B75" s="9"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="9"/>
-      <c r="F75" s="18"/>
+    <row r="75" spans="2:26" ht="15" customHeight="1" thickBot="1">
+      <c r="B75" s="245"/>
+      <c r="C75" s="245"/>
+      <c r="D75" s="245"/>
+      <c r="F75" s="160">
+        <v>46021</v>
+      </c>
       <c r="G75" s="18"/>
       <c r="H75" s="18"/>
       <c r="I75" s="18"/>
@@ -7059,11 +7089,15 @@
       <c r="Y75" s="18"/>
       <c r="Z75" s="18"/>
     </row>
-    <row r="76" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="9"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="9"/>
-      <c r="F76" s="20"/>
+    <row r="76" spans="2:26" ht="15" customHeight="1">
+      <c r="B76" s="228" t="s">
+        <v>89</v>
+      </c>
+      <c r="C76" s="228"/>
+      <c r="D76" s="228"/>
+      <c r="F76" s="19" t="s">
+        <v>91</v>
+      </c>
       <c r="G76" s="18"/>
       <c r="H76" s="18"/>
       <c r="I76" s="18"/>
@@ -7085,12 +7119,12 @@
       <c r="Y76" s="18"/>
       <c r="Z76" s="18"/>
     </row>
-    <row r="77" spans="2:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="216"/>
-      <c r="C77" s="216"/>
-      <c r="D77" s="216"/>
-      <c r="F77" s="217"/>
-      <c r="G77" s="217"/>
+    <row r="77" spans="2:26">
+      <c r="B77" s="9"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="9"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="18"/>
       <c r="H77" s="18"/>
       <c r="I77" s="18"/>
       <c r="J77" s="18"/>
@@ -7111,16 +7145,12 @@
       <c r="Y77" s="18"/>
       <c r="Z77" s="18"/>
     </row>
-    <row r="78" spans="2:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:26" ht="15" customHeight="1">
       <c r="B78" s="9"/>
-      <c r="C78" s="33" t="s">
-        <v>93</v>
-      </c>
+      <c r="C78" s="18"/>
       <c r="D78" s="9"/>
-      <c r="F78" s="238" t="s">
-        <v>168</v>
-      </c>
-      <c r="G78" s="238"/>
+      <c r="F78" s="20"/>
+      <c r="G78" s="18"/>
       <c r="H78" s="18"/>
       <c r="I78" s="18"/>
       <c r="J78" s="18"/>
@@ -7141,15 +7171,12 @@
       <c r="Y78" s="18"/>
       <c r="Z78" s="18"/>
     </row>
-    <row r="79" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="C79" s="32"/>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
+    <row r="79" spans="2:26" ht="15" customHeight="1" thickBot="1">
+      <c r="B79" s="245"/>
+      <c r="C79" s="245"/>
+      <c r="D79" s="245"/>
+      <c r="F79" s="240"/>
+      <c r="G79" s="240"/>
       <c r="H79" s="18"/>
       <c r="I79" s="18"/>
       <c r="J79" s="18"/>
@@ -7170,13 +7197,16 @@
       <c r="Y79" s="18"/>
       <c r="Z79" s="18"/>
     </row>
-    <row r="80" spans="2:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="32"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
+    <row r="80" spans="2:26" ht="15.75" customHeight="1">
+      <c r="B80" s="9"/>
+      <c r="C80" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D80" s="9"/>
+      <c r="F80" s="228" t="s">
+        <v>201</v>
+      </c>
+      <c r="G80" s="228"/>
       <c r="H80" s="18"/>
       <c r="I80" s="18"/>
       <c r="J80" s="18"/>
@@ -7197,75 +7227,102 @@
       <c r="Y80" s="18"/>
       <c r="Z80" s="18"/>
     </row>
-    <row r="81" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="227" t="s">
-        <v>170</v>
-      </c>
-      <c r="C81" s="228"/>
-      <c r="D81" s="228"/>
-      <c r="E81" s="228"/>
-      <c r="F81" s="228"/>
-      <c r="G81" s="229"/>
-      <c r="H81" s="10"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9"/>
-      <c r="K81" s="9"/>
-      <c r="L81" s="9"/>
-      <c r="M81" s="9"/>
-      <c r="N81" s="9"/>
-      <c r="O81" s="9"/>
-      <c r="P81" s="9"/>
-      <c r="Q81" s="9"/>
-      <c r="R81" s="9"/>
-      <c r="S81" s="9"/>
-      <c r="T81" s="9"/>
-      <c r="U81" s="9"/>
-      <c r="V81" s="9"/>
-      <c r="W81" s="9"/>
-      <c r="X81" s="9"/>
-      <c r="Y81" s="9"/>
-      <c r="Z81" s="9"/>
-    </row>
-    <row r="82" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="230" t="s">
-        <v>171</v>
-      </c>
-      <c r="C82" s="231"/>
-      <c r="D82" s="231"/>
-      <c r="E82" s="231"/>
-      <c r="F82" s="231"/>
-      <c r="G82" s="232"/>
-      <c r="H82" s="10"/>
-      <c r="I82" s="37"/>
-      <c r="J82" s="9"/>
-      <c r="K82" s="9"/>
-      <c r="L82" s="9"/>
-      <c r="M82" s="9"/>
-      <c r="N82" s="9"/>
-      <c r="O82" s="9"/>
-      <c r="P82" s="9"/>
-      <c r="Q82" s="9"/>
-      <c r="R82" s="9"/>
-      <c r="S82" s="9"/>
-      <c r="T82" s="9"/>
-      <c r="U82" s="9"/>
-      <c r="V82" s="9"/>
-      <c r="W82" s="9"/>
-      <c r="X82" s="9"/>
-      <c r="Y82" s="9"/>
-      <c r="Z82" s="9"/>
-    </row>
-    <row r="83" spans="2:26" s="10" customFormat="1" ht="156" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="116"/>
-      <c r="C83" s="116"/>
-      <c r="D83" s="116"/>
-      <c r="E83" s="116"/>
-      <c r="F83" s="116"/>
-      <c r="G83" s="117"/>
-    </row>
-    <row r="84" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:26" ht="18" customHeight="1">
+      <c r="B81" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="C81" s="32"/>
+      <c r="D81" s="32"/>
+      <c r="E81" s="32"/>
+      <c r="F81" s="32"/>
+      <c r="G81" s="32"/>
+      <c r="H81" s="18"/>
+      <c r="I81" s="18"/>
+      <c r="J81" s="18"/>
+      <c r="K81" s="18"/>
+      <c r="L81" s="18"/>
+      <c r="M81" s="18"/>
+      <c r="N81" s="18"/>
+      <c r="O81" s="18"/>
+      <c r="P81" s="18"/>
+      <c r="Q81" s="18"/>
+      <c r="R81" s="18"/>
+      <c r="S81" s="18"/>
+      <c r="T81" s="18"/>
+      <c r="U81" s="18"/>
+      <c r="V81" s="18"/>
+      <c r="W81" s="18"/>
+      <c r="X81" s="18"/>
+      <c r="Y81" s="18"/>
+      <c r="Z81" s="18"/>
+    </row>
+    <row r="82" spans="2:26" ht="15.75" thickBot="1">
+      <c r="B82" s="32"/>
+      <c r="C82" s="32"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="32"/>
+      <c r="F82" s="32"/>
+      <c r="G82" s="32"/>
+      <c r="H82" s="18"/>
+      <c r="I82" s="18"/>
+      <c r="J82" s="18"/>
+      <c r="K82" s="18"/>
+      <c r="L82" s="18"/>
+      <c r="M82" s="18"/>
+      <c r="N82" s="18"/>
+      <c r="O82" s="18"/>
+      <c r="P82" s="18"/>
+      <c r="Q82" s="18"/>
+      <c r="R82" s="18"/>
+      <c r="S82" s="18"/>
+      <c r="T82" s="18"/>
+      <c r="U82" s="18"/>
+      <c r="V82" s="18"/>
+      <c r="W82" s="18"/>
+      <c r="X82" s="18"/>
+      <c r="Y82" s="18"/>
+      <c r="Z82" s="18"/>
+    </row>
+    <row r="83" spans="2:26" ht="24" customHeight="1">
+      <c r="B83" s="217" t="s">
+        <v>203</v>
+      </c>
+      <c r="C83" s="218"/>
+      <c r="D83" s="218"/>
+      <c r="E83" s="218"/>
+      <c r="F83" s="218"/>
+      <c r="G83" s="219"/>
+      <c r="H83" s="10"/>
+      <c r="I83" s="9"/>
+      <c r="J83" s="9"/>
+      <c r="K83" s="9"/>
+      <c r="L83" s="9"/>
+      <c r="M83" s="9"/>
+      <c r="N83" s="9"/>
+      <c r="O83" s="9"/>
+      <c r="P83" s="9"/>
+      <c r="Q83" s="9"/>
+      <c r="R83" s="9"/>
+      <c r="S83" s="9"/>
+      <c r="T83" s="9"/>
+      <c r="U83" s="9"/>
+      <c r="V83" s="9"/>
+      <c r="W83" s="9"/>
+      <c r="X83" s="9"/>
+      <c r="Y83" s="9"/>
+      <c r="Z83" s="9"/>
+    </row>
+    <row r="84" spans="2:26" ht="13.5" customHeight="1">
+      <c r="B84" s="220" t="s">
+        <v>204</v>
+      </c>
+      <c r="C84" s="221"/>
+      <c r="D84" s="221"/>
+      <c r="E84" s="221"/>
+      <c r="F84" s="221"/>
+      <c r="G84" s="222"/>
       <c r="H84" s="10"/>
-      <c r="I84" s="9"/>
+      <c r="I84" s="37"/>
       <c r="J84" s="9"/>
       <c r="K84" s="9"/>
       <c r="L84" s="9"/>
@@ -7284,66 +7341,37 @@
       <c r="Y84" s="9"/>
       <c r="Z84" s="9"/>
     </row>
+    <row r="85" spans="2:26" s="10" customFormat="1" ht="156" customHeight="1" thickBot="1">
+      <c r="B85" s="116"/>
+      <c r="C85" s="116"/>
+      <c r="D85" s="116"/>
+      <c r="E85" s="116"/>
+      <c r="F85" s="116"/>
+      <c r="G85" s="117"/>
+    </row>
+    <row r="86" spans="2:26">
+      <c r="H86" s="10"/>
+      <c r="I86" s="9"/>
+      <c r="J86" s="9"/>
+      <c r="K86" s="9"/>
+      <c r="L86" s="9"/>
+      <c r="M86" s="9"/>
+      <c r="N86" s="9"/>
+      <c r="O86" s="9"/>
+      <c r="P86" s="9"/>
+      <c r="Q86" s="9"/>
+      <c r="R86" s="9"/>
+      <c r="S86" s="9"/>
+      <c r="T86" s="9"/>
+      <c r="U86" s="9"/>
+      <c r="V86" s="9"/>
+      <c r="W86" s="9"/>
+      <c r="X86" s="9"/>
+      <c r="Y86" s="9"/>
+      <c r="Z86" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="74">
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="B81:G81"/>
-    <mergeCell ref="B82:G82"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="B42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="B44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="B56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="G56:G57"/>
+  <mergeCells count="75">
     <mergeCell ref="F48:F49"/>
     <mergeCell ref="G48:G49"/>
     <mergeCell ref="B58:C59"/>
@@ -7360,6 +7388,65 @@
     <mergeCell ref="F50:F51"/>
     <mergeCell ref="G50:G51"/>
     <mergeCell ref="B48:C49"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="B56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="B44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="B83:G83"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F23" r:id="rId1" xr:uid="{1A04884D-E1E4-4504-B262-077F3F1E0EF3}"/>
@@ -7391,64 +7478,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D237D29B-37DE-45D6-8EA7-98C4A952DFFE}">
   <dimension ref="D1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="4:4">
       <c r="D1">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:4">
       <c r="D2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:4">
       <c r="D3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:4">
       <c r="D4">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:4">
       <c r="D5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:4">
       <c r="D6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:4">
       <c r="D7">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:4">
       <c r="D8">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:4">
       <c r="D9">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:4">
       <c r="D10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:4">
       <c r="D11">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:4">
       <c r="D12">
         <v>12</v>
       </c>
@@ -7464,134 +7551,134 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:X24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="20" width="5.7109375" style="1" customWidth="1"/>
     <col min="21" max="24" width="8.42578125" style="1" customWidth="1"/>
     <col min="25" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="243" t="s">
-        <v>172</v>
-      </c>
-      <c r="B1" s="243"/>
-      <c r="C1" s="243"/>
-      <c r="D1" s="243"/>
-      <c r="E1" s="243"/>
-      <c r="F1" s="243"/>
-      <c r="G1" s="243"/>
-      <c r="H1" s="243"/>
-      <c r="I1" s="243"/>
-      <c r="J1" s="243"/>
-      <c r="K1" s="243"/>
-      <c r="L1" s="243"/>
-      <c r="M1" s="243"/>
-      <c r="N1" s="243"/>
-      <c r="O1" s="243"/>
-      <c r="P1" s="243"/>
-      <c r="Q1" s="243"/>
-      <c r="R1" s="243"/>
-      <c r="S1" s="243"/>
-      <c r="T1" s="243"/>
-      <c r="U1" s="243" t="s">
-        <v>173</v>
-      </c>
-      <c r="V1" s="243"/>
-      <c r="W1" s="243"/>
-      <c r="X1" s="243"/>
-    </row>
-    <row r="2" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="243"/>
-      <c r="B2" s="243"/>
-      <c r="C2" s="243"/>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="243"/>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="M2" s="243"/>
-      <c r="N2" s="243"/>
-      <c r="O2" s="243"/>
-      <c r="P2" s="243"/>
-      <c r="Q2" s="243"/>
-      <c r="R2" s="243"/>
-      <c r="S2" s="243"/>
-      <c r="T2" s="243"/>
-      <c r="U2" s="251" t="s">
-        <v>174</v>
-      </c>
-      <c r="V2" s="251"/>
-      <c r="W2" s="251"/>
-      <c r="X2" s="251"/>
-    </row>
-    <row r="3" spans="1:24" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="U3" s="252"/>
-      <c r="V3" s="252"/>
-      <c r="W3" s="252"/>
-      <c r="X3" s="252"/>
-    </row>
-    <row r="4" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="248" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="249"/>
-      <c r="C4" s="249"/>
-      <c r="D4" s="249"/>
-      <c r="E4" s="249"/>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
-      <c r="H4" s="249"/>
-      <c r="I4" s="249"/>
-      <c r="J4" s="249"/>
-      <c r="K4" s="249"/>
-      <c r="L4" s="249"/>
-      <c r="M4" s="250"/>
-      <c r="N4" s="248" t="s">
-        <v>176</v>
-      </c>
-      <c r="O4" s="249"/>
-      <c r="P4" s="249"/>
-      <c r="Q4" s="249"/>
-      <c r="R4" s="249"/>
-      <c r="S4" s="249"/>
-      <c r="T4" s="249"/>
-      <c r="U4" s="249"/>
-      <c r="V4" s="249"/>
-      <c r="W4" s="249"/>
-      <c r="X4" s="250"/>
-    </row>
-    <row r="5" spans="1:24" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="245"/>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="M5" s="247"/>
-      <c r="N5" s="245"/>
-      <c r="O5" s="246"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="247"/>
-    </row>
-    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="18.75">
+      <c r="A1" s="274" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" s="274"/>
+      <c r="C1" s="274"/>
+      <c r="D1" s="274"/>
+      <c r="E1" s="274"/>
+      <c r="F1" s="274"/>
+      <c r="G1" s="274"/>
+      <c r="H1" s="274"/>
+      <c r="I1" s="274"/>
+      <c r="J1" s="274"/>
+      <c r="K1" s="274"/>
+      <c r="L1" s="274"/>
+      <c r="M1" s="274"/>
+      <c r="N1" s="274"/>
+      <c r="O1" s="274"/>
+      <c r="P1" s="274"/>
+      <c r="Q1" s="274"/>
+      <c r="R1" s="274"/>
+      <c r="S1" s="274"/>
+      <c r="T1" s="274"/>
+      <c r="U1" s="274" t="s">
+        <v>206</v>
+      </c>
+      <c r="V1" s="274"/>
+      <c r="W1" s="274"/>
+      <c r="X1" s="274"/>
+    </row>
+    <row r="2" spans="1:24" ht="33" customHeight="1">
+      <c r="A2" s="274"/>
+      <c r="B2" s="274"/>
+      <c r="C2" s="274"/>
+      <c r="D2" s="274"/>
+      <c r="E2" s="274"/>
+      <c r="F2" s="274"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="274"/>
+      <c r="I2" s="274"/>
+      <c r="J2" s="274"/>
+      <c r="K2" s="274"/>
+      <c r="L2" s="274"/>
+      <c r="M2" s="274"/>
+      <c r="N2" s="274"/>
+      <c r="O2" s="274"/>
+      <c r="P2" s="274"/>
+      <c r="Q2" s="274"/>
+      <c r="R2" s="274"/>
+      <c r="S2" s="274"/>
+      <c r="T2" s="274"/>
+      <c r="U2" s="254" t="s">
+        <v>207</v>
+      </c>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254"/>
+    </row>
+    <row r="3" spans="1:24" ht="33" customHeight="1" thickBot="1">
+      <c r="U3" s="281"/>
+      <c r="V3" s="281"/>
+      <c r="W3" s="281"/>
+      <c r="X3" s="281"/>
+    </row>
+    <row r="4" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="278" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="279"/>
+      <c r="C4" s="279"/>
+      <c r="D4" s="279"/>
+      <c r="E4" s="279"/>
+      <c r="F4" s="279"/>
+      <c r="G4" s="279"/>
+      <c r="H4" s="279"/>
+      <c r="I4" s="279"/>
+      <c r="J4" s="279"/>
+      <c r="K4" s="279"/>
+      <c r="L4" s="279"/>
+      <c r="M4" s="280"/>
+      <c r="N4" s="278" t="s">
+        <v>209</v>
+      </c>
+      <c r="O4" s="279"/>
+      <c r="P4" s="279"/>
+      <c r="Q4" s="279"/>
+      <c r="R4" s="279"/>
+      <c r="S4" s="279"/>
+      <c r="T4" s="279"/>
+      <c r="U4" s="279"/>
+      <c r="V4" s="279"/>
+      <c r="W4" s="279"/>
+      <c r="X4" s="280"/>
+    </row>
+    <row r="5" spans="1:24" ht="18" customHeight="1" thickBot="1">
+      <c r="A5" s="275"/>
+      <c r="B5" s="276"/>
+      <c r="C5" s="276"/>
+      <c r="D5" s="276"/>
+      <c r="E5" s="276"/>
+      <c r="F5" s="276"/>
+      <c r="G5" s="276"/>
+      <c r="H5" s="276"/>
+      <c r="I5" s="276"/>
+      <c r="J5" s="276"/>
+      <c r="K5" s="276"/>
+      <c r="L5" s="276"/>
+      <c r="M5" s="277"/>
+      <c r="N5" s="275"/>
+      <c r="O5" s="276"/>
+      <c r="P5" s="276"/>
+      <c r="Q5" s="276"/>
+      <c r="R5" s="276"/>
+      <c r="S5" s="276"/>
+      <c r="T5" s="276"/>
+      <c r="U5" s="276"/>
+      <c r="V5" s="276"/>
+      <c r="W5" s="276"/>
+      <c r="X5" s="277"/>
+    </row>
+    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -7617,69 +7704,69 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
-    <row r="7" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="244" t="s">
-        <v>177</v>
-      </c>
-      <c r="B7" s="244"/>
-      <c r="C7" s="244"/>
-      <c r="D7" s="244"/>
-      <c r="E7" s="244"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="244"/>
-      <c r="H7" s="244"/>
-      <c r="I7" s="244"/>
-      <c r="J7" s="244" t="s">
+    <row r="7" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1">
+      <c r="A7" s="252" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" s="252"/>
+      <c r="C7" s="252"/>
+      <c r="D7" s="252"/>
+      <c r="E7" s="252"/>
+      <c r="F7" s="252"/>
+      <c r="G7" s="252"/>
+      <c r="H7" s="252"/>
+      <c r="I7" s="252"/>
+      <c r="J7" s="252" t="s">
         <v>32</v>
       </c>
-      <c r="K7" s="244"/>
-      <c r="L7" s="244"/>
-      <c r="M7" s="244"/>
-      <c r="N7" s="244"/>
-      <c r="O7" s="244"/>
-      <c r="P7" s="244" t="s">
+      <c r="K7" s="252"/>
+      <c r="L7" s="252"/>
+      <c r="M7" s="252"/>
+      <c r="N7" s="252"/>
+      <c r="O7" s="252"/>
+      <c r="P7" s="252" t="s">
         <v>58</v>
       </c>
-      <c r="Q7" s="244"/>
-      <c r="R7" s="244"/>
-      <c r="S7" s="244"/>
-      <c r="T7" s="244"/>
-      <c r="U7" s="244"/>
-      <c r="V7" s="244"/>
-      <c r="W7" s="244"/>
-      <c r="X7" s="244"/>
-    </row>
-    <row r="8" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="253"/>
-      <c r="B8" s="253"/>
-      <c r="C8" s="253"/>
-      <c r="D8" s="253"/>
-      <c r="E8" s="253"/>
-      <c r="F8" s="253"/>
-      <c r="G8" s="253"/>
-      <c r="H8" s="253"/>
-      <c r="I8" s="253"/>
-      <c r="J8" s="254" t="s">
-        <v>178</v>
-      </c>
-      <c r="K8" s="255"/>
-      <c r="L8" s="255"/>
-      <c r="M8" s="255"/>
-      <c r="N8" s="255"/>
-      <c r="O8" s="256"/>
-      <c r="P8" s="254" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q8" s="255"/>
-      <c r="R8" s="255"/>
-      <c r="S8" s="255"/>
-      <c r="T8" s="255"/>
-      <c r="U8" s="255"/>
-      <c r="V8" s="255"/>
-      <c r="W8" s="255"/>
-      <c r="X8" s="256"/>
-    </row>
-    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q7" s="252"/>
+      <c r="R7" s="252"/>
+      <c r="S7" s="252"/>
+      <c r="T7" s="252"/>
+      <c r="U7" s="252"/>
+      <c r="V7" s="252"/>
+      <c r="W7" s="252"/>
+      <c r="X7" s="252"/>
+    </row>
+    <row r="8" spans="1:24" ht="18" customHeight="1">
+      <c r="A8" s="259"/>
+      <c r="B8" s="259"/>
+      <c r="C8" s="259"/>
+      <c r="D8" s="259"/>
+      <c r="E8" s="259"/>
+      <c r="F8" s="259"/>
+      <c r="G8" s="259"/>
+      <c r="H8" s="259"/>
+      <c r="I8" s="259"/>
+      <c r="J8" s="260" t="s">
+        <v>211</v>
+      </c>
+      <c r="K8" s="261"/>
+      <c r="L8" s="261"/>
+      <c r="M8" s="261"/>
+      <c r="N8" s="261"/>
+      <c r="O8" s="262"/>
+      <c r="P8" s="260" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q8" s="261"/>
+      <c r="R8" s="261"/>
+      <c r="S8" s="261"/>
+      <c r="T8" s="261"/>
+      <c r="U8" s="261"/>
+      <c r="V8" s="261"/>
+      <c r="W8" s="261"/>
+      <c r="X8" s="262"/>
+    </row>
+    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -7705,69 +7792,69 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
     </row>
-    <row r="10" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="257" t="s">
-        <v>180</v>
-      </c>
-      <c r="B10" s="257"/>
-      <c r="C10" s="257"/>
-      <c r="D10" s="257"/>
-      <c r="E10" s="257"/>
-      <c r="F10" s="257"/>
-      <c r="G10" s="257"/>
-      <c r="H10" s="257"/>
-      <c r="I10" s="257"/>
-      <c r="J10" s="257"/>
-      <c r="K10" s="257"/>
-      <c r="L10" s="257"/>
-      <c r="M10" s="257"/>
-      <c r="N10" s="257"/>
-      <c r="O10" s="257"/>
-      <c r="P10" s="257"/>
-      <c r="Q10" s="257"/>
-      <c r="R10" s="257"/>
-      <c r="S10" s="257"/>
-      <c r="T10" s="257"/>
-      <c r="U10" s="257"/>
-      <c r="V10" s="257"/>
-      <c r="W10" s="257"/>
-      <c r="X10" s="257"/>
-    </row>
-    <row r="11" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="258" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="258"/>
-      <c r="C11" s="258"/>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258" t="s">
-        <v>181</v>
-      </c>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
-      <c r="M11" s="258" t="s">
-        <v>182</v>
-      </c>
-      <c r="N11" s="258"/>
-      <c r="O11" s="258"/>
-      <c r="P11" s="258"/>
-      <c r="Q11" s="258"/>
-      <c r="R11" s="258"/>
-      <c r="S11" s="258" t="s">
-        <v>183</v>
-      </c>
-      <c r="T11" s="258"/>
-      <c r="U11" s="258"/>
-      <c r="V11" s="258"/>
-      <c r="W11" s="258"/>
-      <c r="X11" s="258"/>
-    </row>
-    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="18" customHeight="1">
+      <c r="A10" s="272" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="272"/>
+      <c r="C10" s="272"/>
+      <c r="D10" s="272"/>
+      <c r="E10" s="272"/>
+      <c r="F10" s="272"/>
+      <c r="G10" s="272"/>
+      <c r="H10" s="272"/>
+      <c r="I10" s="272"/>
+      <c r="J10" s="272"/>
+      <c r="K10" s="272"/>
+      <c r="L10" s="272"/>
+      <c r="M10" s="272"/>
+      <c r="N10" s="272"/>
+      <c r="O10" s="272"/>
+      <c r="P10" s="272"/>
+      <c r="Q10" s="272"/>
+      <c r="R10" s="272"/>
+      <c r="S10" s="272"/>
+      <c r="T10" s="272"/>
+      <c r="U10" s="272"/>
+      <c r="V10" s="272"/>
+      <c r="W10" s="272"/>
+      <c r="X10" s="272"/>
+    </row>
+    <row r="11" spans="1:24" ht="18" customHeight="1">
+      <c r="A11" s="273" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="273"/>
+      <c r="C11" s="273"/>
+      <c r="D11" s="273"/>
+      <c r="E11" s="273"/>
+      <c r="F11" s="273"/>
+      <c r="G11" s="273" t="s">
+        <v>214</v>
+      </c>
+      <c r="H11" s="273"/>
+      <c r="I11" s="273"/>
+      <c r="J11" s="273"/>
+      <c r="K11" s="273"/>
+      <c r="L11" s="273"/>
+      <c r="M11" s="273" t="s">
+        <v>215</v>
+      </c>
+      <c r="N11" s="273"/>
+      <c r="O11" s="273"/>
+      <c r="P11" s="273"/>
+      <c r="Q11" s="273"/>
+      <c r="R11" s="273"/>
+      <c r="S11" s="273" t="s">
+        <v>216</v>
+      </c>
+      <c r="T11" s="273"/>
+      <c r="U11" s="273"/>
+      <c r="V11" s="273"/>
+      <c r="W11" s="273"/>
+      <c r="X11" s="273"/>
+    </row>
+    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -7793,69 +7880,69 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="244" t="s">
-        <v>184</v>
-      </c>
-      <c r="B13" s="244"/>
-      <c r="C13" s="244"/>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="244"/>
-      <c r="G13" s="244"/>
-      <c r="H13" s="244"/>
-      <c r="I13" s="244"/>
-      <c r="J13" s="244" t="s">
+    <row r="13" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1">
+      <c r="A13" s="252" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="252"/>
+      <c r="C13" s="252"/>
+      <c r="D13" s="252"/>
+      <c r="E13" s="252"/>
+      <c r="F13" s="252"/>
+      <c r="G13" s="252"/>
+      <c r="H13" s="252"/>
+      <c r="I13" s="252"/>
+      <c r="J13" s="252" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="244"/>
-      <c r="L13" s="244"/>
-      <c r="M13" s="244"/>
-      <c r="N13" s="244"/>
-      <c r="O13" s="244"/>
-      <c r="P13" s="244" t="s">
+      <c r="K13" s="252"/>
+      <c r="L13" s="252"/>
+      <c r="M13" s="252"/>
+      <c r="N13" s="252"/>
+      <c r="O13" s="252"/>
+      <c r="P13" s="252" t="s">
         <v>58</v>
       </c>
-      <c r="Q13" s="244"/>
-      <c r="R13" s="244"/>
-      <c r="S13" s="244"/>
-      <c r="T13" s="244"/>
-      <c r="U13" s="244"/>
-      <c r="V13" s="244"/>
-      <c r="W13" s="244"/>
-      <c r="X13" s="244"/>
-    </row>
-    <row r="14" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="253"/>
-      <c r="B14" s="253"/>
-      <c r="C14" s="253"/>
-      <c r="D14" s="253"/>
-      <c r="E14" s="253"/>
-      <c r="F14" s="253"/>
-      <c r="G14" s="253"/>
-      <c r="H14" s="253"/>
-      <c r="I14" s="253"/>
-      <c r="J14" s="254" t="s">
-        <v>185</v>
-      </c>
-      <c r="K14" s="255"/>
-      <c r="L14" s="255"/>
-      <c r="M14" s="255"/>
-      <c r="N14" s="255"/>
-      <c r="O14" s="256"/>
-      <c r="P14" s="254" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q14" s="255"/>
-      <c r="R14" s="255"/>
-      <c r="S14" s="255"/>
-      <c r="T14" s="255"/>
-      <c r="U14" s="255"/>
-      <c r="V14" s="255"/>
-      <c r="W14" s="255"/>
-      <c r="X14" s="256"/>
-    </row>
-    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q13" s="252"/>
+      <c r="R13" s="252"/>
+      <c r="S13" s="252"/>
+      <c r="T13" s="252"/>
+      <c r="U13" s="252"/>
+      <c r="V13" s="252"/>
+      <c r="W13" s="252"/>
+      <c r="X13" s="252"/>
+    </row>
+    <row r="14" spans="1:24" ht="18" customHeight="1">
+      <c r="A14" s="259"/>
+      <c r="B14" s="259"/>
+      <c r="C14" s="259"/>
+      <c r="D14" s="259"/>
+      <c r="E14" s="259"/>
+      <c r="F14" s="259"/>
+      <c r="G14" s="259"/>
+      <c r="H14" s="259"/>
+      <c r="I14" s="259"/>
+      <c r="J14" s="260" t="s">
+        <v>218</v>
+      </c>
+      <c r="K14" s="261"/>
+      <c r="L14" s="261"/>
+      <c r="M14" s="261"/>
+      <c r="N14" s="261"/>
+      <c r="O14" s="262"/>
+      <c r="P14" s="260" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q14" s="261"/>
+      <c r="R14" s="261"/>
+      <c r="S14" s="261"/>
+      <c r="T14" s="261"/>
+      <c r="U14" s="261"/>
+      <c r="V14" s="261"/>
+      <c r="W14" s="261"/>
+      <c r="X14" s="262"/>
+    </row>
+    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -7881,173 +7968,185 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
     </row>
-    <row r="16" spans="1:24" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="264" t="s">
-        <v>187</v>
-      </c>
-      <c r="B16" s="264"/>
-      <c r="C16" s="264"/>
-      <c r="D16" s="264"/>
-      <c r="E16" s="264"/>
-      <c r="F16" s="264"/>
-      <c r="G16" s="264"/>
-      <c r="H16" s="264"/>
-      <c r="I16" s="264"/>
-      <c r="J16" s="265" t="s">
-        <v>188</v>
-      </c>
-      <c r="K16" s="265"/>
-      <c r="L16" s="265"/>
-      <c r="M16" s="265"/>
-      <c r="N16" s="264" t="s">
-        <v>189</v>
-      </c>
-      <c r="O16" s="264"/>
-      <c r="P16" s="264"/>
-      <c r="Q16" s="264"/>
-      <c r="R16" s="264"/>
-      <c r="S16" s="264"/>
-      <c r="T16" s="266" t="s">
-        <v>190</v>
-      </c>
-      <c r="U16" s="266"/>
-      <c r="V16" s="266"/>
-      <c r="W16" s="266"/>
-      <c r="X16" s="266"/>
-    </row>
-    <row r="17" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="259" t="s">
-        <v>191</v>
-      </c>
-      <c r="B17" s="251"/>
-      <c r="C17" s="251"/>
-      <c r="D17" s="251"/>
-      <c r="E17" s="251"/>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="260"/>
-      <c r="J17" s="267" t="s">
-        <v>192</v>
-      </c>
-      <c r="K17" s="268"/>
-      <c r="L17" s="268"/>
-      <c r="M17" s="269"/>
-      <c r="N17" s="259" t="s">
-        <v>193</v>
-      </c>
-      <c r="O17" s="251"/>
-      <c r="P17" s="251"/>
-      <c r="Q17" s="251"/>
-      <c r="R17" s="251"/>
-      <c r="S17" s="260"/>
-      <c r="T17" s="259" t="s">
-        <v>194</v>
-      </c>
-      <c r="U17" s="251"/>
-      <c r="V17" s="251"/>
-      <c r="W17" s="251"/>
-      <c r="X17" s="260"/>
-    </row>
-    <row r="18" spans="1:24" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="261"/>
-      <c r="B18" s="262"/>
-      <c r="C18" s="262"/>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="262"/>
-      <c r="G18" s="262"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="263"/>
-      <c r="J18" s="270"/>
-      <c r="K18" s="271"/>
-      <c r="L18" s="271"/>
-      <c r="M18" s="272"/>
-      <c r="N18" s="261"/>
-      <c r="O18" s="262"/>
-      <c r="P18" s="262"/>
-      <c r="Q18" s="262"/>
-      <c r="R18" s="262"/>
-      <c r="S18" s="263"/>
-      <c r="T18" s="261"/>
-      <c r="U18" s="262"/>
-      <c r="V18" s="262"/>
-      <c r="W18" s="262"/>
-      <c r="X18" s="263"/>
-    </row>
-    <row r="19" spans="1:24" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:24" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A21" s="276" t="s">
-        <v>195</v>
-      </c>
-      <c r="B21" s="276"/>
-      <c r="C21" s="276"/>
-      <c r="D21" s="276"/>
-      <c r="E21" s="276"/>
-      <c r="F21" s="276"/>
-      <c r="G21" s="276"/>
-      <c r="H21" s="276"/>
+    <row r="16" spans="1:24" s="4" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A16" s="263" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" s="263"/>
+      <c r="C16" s="263"/>
+      <c r="D16" s="263"/>
+      <c r="E16" s="263"/>
+      <c r="F16" s="263"/>
+      <c r="G16" s="263"/>
+      <c r="H16" s="263"/>
+      <c r="I16" s="263"/>
+      <c r="J16" s="264" t="s">
+        <v>221</v>
+      </c>
+      <c r="K16" s="264"/>
+      <c r="L16" s="264"/>
+      <c r="M16" s="264"/>
+      <c r="N16" s="263" t="s">
+        <v>222</v>
+      </c>
+      <c r="O16" s="263"/>
+      <c r="P16" s="263"/>
+      <c r="Q16" s="263"/>
+      <c r="R16" s="263"/>
+      <c r="S16" s="263"/>
+      <c r="T16" s="265" t="s">
+        <v>223</v>
+      </c>
+      <c r="U16" s="265"/>
+      <c r="V16" s="265"/>
+      <c r="W16" s="265"/>
+      <c r="X16" s="265"/>
+    </row>
+    <row r="17" spans="1:24" ht="18" customHeight="1">
+      <c r="A17" s="253" t="s">
+        <v>224</v>
+      </c>
+      <c r="B17" s="254"/>
+      <c r="C17" s="254"/>
+      <c r="D17" s="254"/>
+      <c r="E17" s="254"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="255"/>
+      <c r="J17" s="266" t="s">
+        <v>225</v>
+      </c>
+      <c r="K17" s="267"/>
+      <c r="L17" s="267"/>
+      <c r="M17" s="268"/>
+      <c r="N17" s="253" t="s">
+        <v>226</v>
+      </c>
+      <c r="O17" s="254"/>
+      <c r="P17" s="254"/>
+      <c r="Q17" s="254"/>
+      <c r="R17" s="254"/>
+      <c r="S17" s="255"/>
+      <c r="T17" s="253" t="s">
+        <v>227</v>
+      </c>
+      <c r="U17" s="254"/>
+      <c r="V17" s="254"/>
+      <c r="W17" s="254"/>
+      <c r="X17" s="255"/>
+    </row>
+    <row r="18" spans="1:24" ht="48.75" customHeight="1">
+      <c r="A18" s="256"/>
+      <c r="B18" s="257"/>
+      <c r="C18" s="257"/>
+      <c r="D18" s="257"/>
+      <c r="E18" s="257"/>
+      <c r="F18" s="257"/>
+      <c r="G18" s="257"/>
+      <c r="H18" s="257"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="269"/>
+      <c r="K18" s="270"/>
+      <c r="L18" s="270"/>
+      <c r="M18" s="271"/>
+      <c r="N18" s="256"/>
+      <c r="O18" s="257"/>
+      <c r="P18" s="257"/>
+      <c r="Q18" s="257"/>
+      <c r="R18" s="257"/>
+      <c r="S18" s="258"/>
+      <c r="T18" s="256"/>
+      <c r="U18" s="257"/>
+      <c r="V18" s="257"/>
+      <c r="W18" s="257"/>
+      <c r="X18" s="258"/>
+    </row>
+    <row r="19" spans="1:24" ht="39" customHeight="1"/>
+    <row r="20" spans="1:24" ht="39" customHeight="1"/>
+    <row r="21" spans="1:24">
+      <c r="A21" s="251" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" s="251"/>
+      <c r="C21" s="251"/>
+      <c r="D21" s="251"/>
+      <c r="E21" s="251"/>
+      <c r="F21" s="251"/>
+      <c r="G21" s="251"/>
+      <c r="H21" s="251"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="276" t="s">
-        <v>196</v>
-      </c>
-      <c r="K21" s="276"/>
-      <c r="L21" s="276"/>
-      <c r="M21" s="276"/>
-      <c r="N21" s="276"/>
-      <c r="O21" s="276"/>
-      <c r="P21" s="276"/>
+      <c r="J21" s="251" t="s">
+        <v>229</v>
+      </c>
+      <c r="K21" s="251"/>
+      <c r="L21" s="251"/>
+      <c r="M21" s="251"/>
+      <c r="N21" s="251"/>
+      <c r="O21" s="251"/>
+      <c r="P21" s="251"/>
       <c r="Q21" s="6"/>
-      <c r="R21" s="276" t="s">
-        <v>197</v>
-      </c>
-      <c r="S21" s="276"/>
-      <c r="T21" s="276"/>
-      <c r="U21" s="276"/>
-      <c r="V21" s="276"/>
-      <c r="W21" s="276"/>
-      <c r="X21" s="276"/>
-    </row>
-    <row r="23" spans="1:24" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P23" s="273" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q23" s="273"/>
-      <c r="R23" s="273"/>
-      <c r="S23" s="273"/>
-      <c r="T23" s="273"/>
-      <c r="U23" s="274" t="s">
-        <v>199</v>
-      </c>
-      <c r="V23" s="274"/>
-      <c r="W23" s="274"/>
-      <c r="X23" s="274"/>
-    </row>
-    <row r="24" spans="1:24" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P24" s="273" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q24" s="273"/>
-      <c r="R24" s="273"/>
-      <c r="S24" s="273"/>
-      <c r="T24" s="273"/>
-      <c r="U24" s="275" t="s">
-        <v>201</v>
-      </c>
-      <c r="V24" s="275"/>
-      <c r="W24" s="275"/>
-      <c r="X24" s="275"/>
+      <c r="R21" s="251" t="s">
+        <v>230</v>
+      </c>
+      <c r="S21" s="251"/>
+      <c r="T21" s="251"/>
+      <c r="U21" s="251"/>
+      <c r="V21" s="251"/>
+      <c r="W21" s="251"/>
+      <c r="X21" s="251"/>
+    </row>
+    <row r="23" spans="1:24" ht="38.25" customHeight="1">
+      <c r="P23" s="248" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q23" s="248"/>
+      <c r="R23" s="248"/>
+      <c r="S23" s="248"/>
+      <c r="T23" s="248"/>
+      <c r="U23" s="249" t="s">
+        <v>232</v>
+      </c>
+      <c r="V23" s="249"/>
+      <c r="W23" s="249"/>
+      <c r="X23" s="249"/>
+    </row>
+    <row r="24" spans="1:24" ht="38.25" customHeight="1">
+      <c r="P24" s="248" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q24" s="248"/>
+      <c r="R24" s="248"/>
+      <c r="S24" s="248"/>
+      <c r="T24" s="248"/>
+      <c r="U24" s="250" t="s">
+        <v>234</v>
+      </c>
+      <c r="V24" s="250"/>
+      <c r="W24" s="250"/>
+      <c r="X24" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="P23:T23"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="P24:T24"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="R21:X21"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="U1:X1"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="P7:X7"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:X4"/>
+    <mergeCell ref="N5:X5"/>
+    <mergeCell ref="U2:X3"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="P8:X8"/>
+    <mergeCell ref="A10:X10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="M11:R11"/>
+    <mergeCell ref="S11:X11"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="J13:O13"/>
     <mergeCell ref="P13:X13"/>
@@ -8062,25 +8161,13 @@
     <mergeCell ref="T16:X16"/>
     <mergeCell ref="A17:I18"/>
     <mergeCell ref="J17:M18"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="P8:X8"/>
-    <mergeCell ref="A10:X10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="M11:R11"/>
-    <mergeCell ref="S11:X11"/>
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="J7:O7"/>
-    <mergeCell ref="P7:X7"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="N4:X4"/>
-    <mergeCell ref="N5:X5"/>
-    <mergeCell ref="U2:X3"/>
+    <mergeCell ref="P23:T23"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="P24:T24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="R21:X21"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="95" orientation="landscape" horizontalDpi="4294967294" verticalDpi="200" r:id="rId1"/>
